--- a/workspaces/btc_daily_14days/macd/macd_12_26.xlsx
+++ b/workspaces/btc_daily_14days/macd/macd_12_26.xlsx
@@ -575,46 +575,46 @@
         <v>6</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.485526931093887</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.106009877880417</v>
+        <v>-4.09303659666206</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.502061736797074</v>
+        <v>-4.487884606152988</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.30613645128935</v>
+        <v>12.26671485354237</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>28.45315295836457</v>
+        <v>28.36258082976286</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>28.75788152910826</v>
+        <v>28.66647858034037</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>28.680169625738</v>
+        <v>28.58878657165889</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>28.2190040939875</v>
+        <v>28.12949972312509</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>28.16482863686119</v>
+        <v>28.07542261514059</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>27.31984889356734</v>
+        <v>27.23294456954493</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>43.82881198396046</v>
+        <v>43.68943341988229</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.4513196257648</v>
+        <v>10.4174344192175</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>26.74799914898799</v>
+        <v>26.66248128651191</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>43.72464226105087</v>
+        <v>43.5854475825754</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>17</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>12.21244403272853</v>
+        <v>12.17358889181853</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>16.48726222313368</v>
+        <v>16.43475701467366</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>27.86671866484453</v>
+        <v>27.77794083190757</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.457284868030328</v>
+        <v>4.442625359848918</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9.807596872100362</v>
+        <v>9.775866337562974</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.10779541991927</v>
+        <v>10.07524380602251</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>15.91655748107413</v>
+        <v>15.86528832211349</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>15.45229526030747</v>
+        <v>15.40292522203787</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.286668710632036</v>
+        <v>-2.279646444629122</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.65159710959162</v>
+        <v>8.623627279629204</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>26.13904214918641</v>
+        <v>26.05518789972292</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>26.1801201551697</v>
+        <v>26.09597692544639</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.066099788999786</v>
+        <v>8.039567671093884</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.318605662437761</v>
+        <v>8.291329935519258</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>19</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.125017267575998</v>
+        <v>-5.108770757361064</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-17.26713570423232</v>
+        <v>-17.21215825941974</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-12.40065013970708</v>
+        <v>-12.36143786379361</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-7.006253707355846</v>
+        <v>-6.98438227846259</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.278512920304586</v>
+        <v>-2.271872697629661</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-7.250906420251766</v>
+        <v>-7.228232630503761</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-23.15018397276533</v>
+        <v>-23.07697048740548</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-18.35181059396994</v>
+        <v>-18.29351124608421</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-13.14398771143812</v>
+        <v>-13.10218120224819</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-8.724163021457642</v>
+        <v>-8.696812318129773</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-8.931180338045458</v>
+        <v>-8.903621515097633</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.898693651235291</v>
+        <v>-8.87139889246788</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.043735311164014</v>
+        <v>-4.031774759926257</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.794193305355819</v>
+        <v>-3.782973470058572</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>21</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.41132358455193</v>
+        <v>9.381001704391977</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-6.48756960830206</v>
+        <v>-6.466700784027751</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.17284676359301</v>
+        <v>12.13345197503975</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.540828825661805</v>
+        <v>7.516152970729117</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-16.82926641828221</v>
+        <v>-16.77578509660549</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-16.53565529552915</v>
+        <v>-16.48291011928847</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-26.16250632259785</v>
+        <v>-26.07888513942351</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-21.86697763941932</v>
+        <v>-21.7968016482309</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.619529020264423</v>
+        <v>-7.595068134861521</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-8.473165145247187</v>
+        <v>-8.446350778284739</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.680142690348347</v>
+        <v>-8.653118273066092</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-13.42250541547097</v>
+        <v>-13.38039825727416</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-13.84737151384963</v>
+        <v>-13.80377750745184</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.045739479504803</v>
+        <v>-4.033600036472215</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>12</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-10.82677165353952</v>
+        <v>-10.79208990868646</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-20.77684099870579</v>
+        <v>-20.7097298134963</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-21.17697953805839</v>
+        <v>-21.10917003249411</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-21.05182743740375</v>
+        <v>-20.98451662858916</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-29.93764353871929</v>
+        <v>-29.84146038514979</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-21.30363877156391</v>
+        <v>-21.23508893858188</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-13.04806857171693</v>
+        <v>-13.00604664243915</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.176190814400471</v>
+        <v>3.166196819925339</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.233966580929952</v>
+        <v>-5.216997040393821</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-14.43901466181865</v>
+        <v>-14.39274570213706</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.293441050477867</v>
+        <v>-6.273890669784315</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-14.61653072296312</v>
+        <v>-14.5702291537507</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-15.04173169805214</v>
+        <v>-14.99393003178147</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-14.79478167945702</v>
+        <v>-14.74788575075415</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>31</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.571077808822288</v>
+        <v>5.552852598419562</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.733856193682108</v>
+        <v>0.7317963510100256</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.56645976666961</v>
+        <v>3.554601963510585</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4695189413766556</v>
+        <v>0.467626266522565</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>9.617712898849661</v>
+        <v>9.586406985163464</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.228362490674904</v>
+        <v>0.2276875364609623</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.374199694931299</v>
+        <v>3.363314214934292</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.555959776690344</v>
+        <v>-3.544187158835307</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3856749758240028</v>
+        <v>-0.3842760677852013</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.470699260568935</v>
+        <v>-4.456321961714806</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.442769350925694</v>
+        <v>-1.438769599007799</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.408596030921629</v>
+        <v>-1.404711903229476</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.40497132036618</v>
+        <v>1.399848300913021</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.892337374425523</v>
+        <v>4.875770163219094</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.268466441692617</v>
+        <v>2.379110907978088</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>17.32791234315624</v>
+        <v>18.13928316536084</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>21.7016149487563</v>
+        <v>22.72862284698056</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>19.45472749377523</v>
+        <v>20.37623885372142</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>18.92068460610126</v>
+        <v>19.81584818274399</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>14.45524441967198</v>
+        <v>15.13493921671741</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9.604933380547898</v>
+        <v>10.0572515157405</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>13.90952028002214</v>
+        <v>14.55992667812807</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>11.46621540058361</v>
+        <v>12.00380513224773</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>8.230802607686954</v>
+        <v>8.618872780581498</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>10.41508254043363</v>
+        <v>10.91497322678124</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.677083008709772</v>
+        <v>5.953975848712531</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>13.76687693615455</v>
+        <v>14.42371822823726</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.413162502313973</v>
+        <v>3.585447582575398</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.244266597823561</v>
+        <v>3.34985226104591</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>8.192194206882519</v>
+        <v>8.453107437399559</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7.799378890160497</v>
+        <v>8.055944966651488</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2712253587893301</v>
+        <v>-0.2695265049266453</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.753894761385624</v>
+        <v>5.944459499810826</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9.335966820682017</v>
+        <v>9.634380487297918</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7.611617568866635</v>
+        <v>7.854742206358281</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>10.43006875551068</v>
+        <v>10.76034532825084</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.44353554884345</v>
+        <v>5.617365755511692</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>9.522335915114155</v>
+        <v>9.825514297900597</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.664614278417716</v>
+        <v>3.790012363691552</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>11.19154087312629</v>
+        <v>11.55259103073553</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.852704883665268</v>
+        <v>6.047590657078771</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.809959905436862</v>
+        <v>2.907481480881259</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-7.210419452285443</v>
+        <v>-7.331071754930157</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-10.71151480513432</v>
+        <v>-10.89107040151342</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-18.66028576772948</v>
+        <v>-18.97152215480639</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-16.64651228448137</v>
+        <v>-16.92575873222405</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.857134269386947</v>
+        <v>-5.950707184009204</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1068804668284287</v>
+        <v>0.1135398284840221</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.757457137456299</v>
+        <v>-3.817904256603207</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-11.78736512886088</v>
+        <v>-11.98536624976658</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-11.85162479608067</v>
+        <v>-12.05168277429804</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-21.10148463268953</v>
+        <v>-21.45826435640009</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-19.4142139299103</v>
+        <v>-19.73994075763989</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-15.60010832938646</v>
+        <v>-15.8594037541406</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-16.01300940160932</v>
+        <v>-16.2796583650855</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-13.87515709214863</v>
+        <v>-14.10686010973317</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.928248426777976</v>
+        <v>2.959080022395831</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.72732348960448</v>
+        <v>3.766508815509603</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.333333392967766</v>
+        <v>3.369967874723841</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4.670321966983188</v>
+        <v>4.719522672863185</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.132822824749468</v>
+        <v>4.178665773973201</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.431810388831529</v>
+        <v>4.480476546920379</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.4789563204520277</v>
+        <v>-0.4820809969614288</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.568511310710889</v>
+        <v>-4.615046174624069</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.86513587547865</v>
+        <v>0.8740371888538476</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.438185293104027</v>
+        <v>2.462936394070368</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.026898693056943</v>
+        <v>1.038670874630839</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1473794361046998</v>
+        <v>-0.1464581631462281</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.977242580995188</v>
+        <v>-3.005737164335031</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.522317979725244</v>
+        <v>-1.536503636936239</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.249343832020998</v>
+        <v>-5.411537730390705</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-13.16370834172807</v>
+        <v>-13.57561993417646</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-7.259616613002763</v>
+        <v>-7.480086138454091</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-4.767092371190877</v>
+        <v>-4.911524785673137</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-4.876323993549093</v>
+        <v>-5.017733427384954</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-5.729676871808749</v>
+        <v>-5.898717216862117</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.015971229836168</v>
+        <v>-3.106121734205189</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.244526187902451</v>
+        <v>-2.316995445288867</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.093578035651255</v>
+        <v>-3.191003461552654</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.341440181894193</v>
+        <v>-2.415112386418173</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.543741089119372</v>
+        <v>-2.619865710735937</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.1492894088949868</v>
+        <v>-0.1464581631462281</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.918167929620729</v>
+        <v>-3.005737164334668</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.053325393141257</v>
+        <v>2.122032948428689</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.380603731273673</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.520182905009257</v>
+        <v>1.546375754537117</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.5915538990742988</v>
+        <v>-0.6030617966267116</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.08313756538665018</v>
+        <v>-0.08391322144887425</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.581176809941752</v>
+        <v>3.663379849193404</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.02168469339496</v>
+        <v>-1.039178213090942</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.101797480936007</v>
+        <v>-1.12391193036337</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.953719489126314</v>
+        <v>-3.019666757716799</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.9162396611901116</v>
+        <v>-0.9378095010417837</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-5.245539856229719</v>
+        <v>-5.359363257497961</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-5.448560331898406</v>
+        <v>-5.564116581815711</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-6.118098803584587</v>
+        <v>-6.244019138755988</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-7.224946557069927</v>
+        <v>-7.378559463986932</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-5.584710453221589</v>
+        <v>-5.700266703138894</v>
       </c>
     </row>
     <row r="18">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.1082</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4094~4107</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4094</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.00230066201549306</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.1015</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4088~4101</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4088</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.005952072377198192</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.09482</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4071~4084</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4071</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.04485849650771456</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.08814</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4052~4065</t>
-        </is>
+      <c r="B9" t="n">
+        <v>4052</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.02111359696274206</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.08145</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4031~4044</t>
-        </is>
+      <c r="B10" t="n">
+        <v>4031</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.07009509567980388</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.07477</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>4019~4032</t>
-        </is>
+      <c r="B11" t="n">
+        <v>4019</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.03808117735283645</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.06809</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3988~4001</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3988</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.08154129446641889</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.06141</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3948~3959</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3948</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.1064719145519746</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.05472</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3889~3898</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3889</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.1589077917338315</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.04804</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3837~3845</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3837</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.061708801354321</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.04136</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3755~3762</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3755</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.1276754281312904</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.03467</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3632~3635</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3632</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.05126594388906369</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.02799</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3492~3492</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3492</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.002029385502069658</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.02131</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3284~3284</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3284</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.3080233119459379</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.01463</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3038~3038</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3038</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.6007025619493405</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; -0.007942</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2758~2758</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2758</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.914828539833529</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; -0.00126</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2406~2406</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2406</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2.24471629325636</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.005423</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2063~2063</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2063</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.94185009471974</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.01211</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1785~1785</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1785</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2.408522464103754</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.01879</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1473~1473</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1473</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>3.378930994114533</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.02547</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1152~1152</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1152</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>3.322533902012246</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.03215</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>923~923</t>
-        </is>
+      <c r="B27" t="n">
+        <v>923</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>3.411220401350157</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.03884</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>742~742</t>
-        </is>
+      <c r="B28" t="n">
+        <v>742</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>3.840793485719949</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.04552</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>588~588</t>
-        </is>
+      <c r="B29" t="n">
+        <v>588</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>3.118806577749211</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.0522</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>447~447</t>
-        </is>
+      <c r="B30" t="n">
+        <v>447</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>5.000968838626719</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.05889</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>343~343</t>
-        </is>
+      <c r="B31" t="n">
+        <v>343</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>3.77478325413405</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.06557</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>246~246</t>
-        </is>
+      <c r="B32" t="n">
+        <v>246</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>2.791114525318484</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.07225</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>189~189</t>
-        </is>
+      <c r="B33" t="n">
+        <v>189</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>3.062117235345582</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.07893</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>124~124</t>
-        </is>
+      <c r="B34" t="n">
+        <v>124</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.07408348150030264</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.08562</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-1.302962129733785</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.1082</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.1124859392575885</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.1015</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>90~90</t>
-        </is>
+      <c r="B7" t="n">
+        <v>90</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.2712160979877467</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.09482</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>107~107</t>
-        </is>
+      <c r="B8" t="n">
+        <v>107</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1.712169156425531</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.08814</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>126~126</t>
-        </is>
+      <c r="B9" t="n">
+        <v>126</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.6811648543932023</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.08145</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>147~147</t>
-        </is>
+      <c r="B10" t="n">
+        <v>147</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1.928330387273022</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.07477</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>159~159</t>
-        </is>
+      <c r="B11" t="n">
+        <v>159</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.9656811766453686</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.06809</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>190~190</t>
-        </is>
+      <c r="B12" t="n">
+        <v>190</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1.717087995579497</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.06141</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>230~232</t>
-        </is>
+      <c r="B13" t="n">
+        <v>230</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.816906507376231</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.05472</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>289~293</t>
-        </is>
+      <c r="B14" t="n">
+        <v>289</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2.114070212213235</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.04804</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>341~346</t>
-        </is>
+      <c r="B15" t="n">
+        <v>341</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.6857524312351089</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.04136</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>423~429</t>
-        </is>
+      <c r="B16" t="n">
+        <v>423</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.11961529284364</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.03467</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>546~556</t>
-        </is>
+      <c r="B17" t="n">
+        <v>546</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.335164938915014</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.02799</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>686~699</t>
-        </is>
+      <c r="B18" t="n">
+        <v>686</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.01013821770132495</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.02131</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>894~907</t>
-        </is>
+      <c r="B19" t="n">
+        <v>894</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.115268529691782</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.01463</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1140~1153</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1140</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.58277049713972</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; -0.007942</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1420~1433</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1420</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.760709778688685</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; -0.00126</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1772~1785</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1772</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-3.025651205364035</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.005423</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2115~2128</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2115</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.882536064570871</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.01211</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2393~2406</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2393</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.786871404166746</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.01879</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2705~2718</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2705</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.831186664580834</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.02547</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3026~3039</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3026</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.259479781216889</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.03215</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3255~3268</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3255</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.963450560112058</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.03884</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3436~3449</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3436</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.826288421688659</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.04552</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3590~3603</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3590</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.5089809235960416</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.0522</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3731~3744</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3731</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.5970707988424522</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.05889</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3835~3848</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3835</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.3364736632453216</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.06557</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3932~3945</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3932</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.1740466852289799</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.07225</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3989~4002</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3989</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.1446127330035836</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.07893</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4054~4067</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4054</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.002258753800354896</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.08562</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4094~4107</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4094</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.02664933501281297</v>

--- a/workspaces/btc_daily_14days/macd/macd_12_26.xlsx
+++ b/workspaces/btc_daily_14days/macd/macd_12_26.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MACD-12-26 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MACD-12-26 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>6</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.485526931093887</v>
+        <v>-2.473047068800405</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.09303659666206</v>
+        <v>-4.080168245833555</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.487884606152988</v>
+        <v>-4.474915992290754</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.26671485354237</v>
+        <v>12.27966915898204</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>28.36258082976286</v>
+        <v>28.37567761561089</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>28.66647858034037</v>
+        <v>28.67950925238171</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>28.58878657165889</v>
+        <v>28.60184211343055</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>28.12949972312509</v>
+        <v>28.14267111764402</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>28.07542261514059</v>
+        <v>28.08861331529906</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>27.23294456954493</v>
+        <v>27.24634288392284</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>43.68943341988229</v>
+        <v>43.702888530593</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.4174344192175</v>
+        <v>10.43088129927875</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>26.66248128651191</v>
+        <v>26.67603557254408</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>43.5854475825754</v>
+        <v>43.57501794687725</v>
       </c>
     </row>
     <row r="7">
@@ -627,98 +627,98 @@
         <v>17</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>12.17358889181853</v>
+        <v>12.18607996358072</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>16.43475701467366</v>
+        <v>16.44763993165233</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>27.77794083190757</v>
+        <v>27.79093056501788</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.442625359848918</v>
+        <v>4.455574859070524</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9.775866337562974</v>
+        <v>9.788953062418337</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.07524380602251</v>
+        <v>10.08826553263467</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>15.86528832211349</v>
+        <v>15.87833850811961</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>15.40292522203787</v>
+        <v>15.41609201999957</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.279646444629122</v>
+        <v>-2.266464886668601</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.623627279629204</v>
+        <v>8.63702110667127</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>26.05518789972292</v>
+        <v>26.06863985374963</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>26.09597692544639</v>
+        <v>26.10942567286163</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.039567671093884</v>
+        <v>8.053120833178312</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.291329935519258</v>
+        <v>8.280900299821106</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.09148</t>
+          <t>X ≈ -0.09147</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>19</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.108770757361064</v>
+        <v>-5.096293513813968</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-17.21215825941974</v>
+        <v>-17.19929998767974</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-12.36143786379361</v>
+        <v>-12.34847493326325</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.98438227846259</v>
+        <v>-6.971439958141858</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.271872697629661</v>
+        <v>-2.258792725914937</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-7.228232630503761</v>
+        <v>-7.215219460153371</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-23.07697048740548</v>
+        <v>-23.06393695351243</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-18.29351124608421</v>
+        <v>-18.2803568169679</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-13.10218120224819</v>
+        <v>-13.08900309353646</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-8.696812318129773</v>
+        <v>-8.683422787001881</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-8.903621515097633</v>
+        <v>-8.89017594739969</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.87139889246788</v>
+        <v>-8.857954404433571</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.031774759926257</v>
+        <v>-4.018222353841551</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.782973470058572</v>
+        <v>-3.793403105756724</v>
       </c>
     </row>
     <row r="9">
@@ -731,202 +731,202 @@
         <v>21</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.381001704391977</v>
+        <v>9.393490015079188</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-6.466700784027751</v>
+        <v>-6.453835236479549</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.13345197503975</v>
+        <v>12.14643091983282</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.516152970729117</v>
+        <v>7.529103785039794</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-16.77578509660549</v>
+        <v>-16.76271345494248</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-16.48291011928847</v>
+        <v>-16.46990182381921</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-26.07888513942351</v>
+        <v>-26.06585331707878</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-21.7968016482309</v>
+        <v>-21.78364883990423</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.595068134861521</v>
+        <v>-7.581888578001049</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-8.446350778284739</v>
+        <v>-8.432961360844935</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.653118273066092</v>
+        <v>-8.639672791043679</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-13.38039825727416</v>
+        <v>-13.36695441149731</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-13.80377750745184</v>
+        <v>-13.79022574082717</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.033600036472215</v>
+        <v>-4.044029672168207</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.07811</t>
+          <t>X ≈ -0.0781</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>12</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-10.79208990868646</v>
+        <v>-10.77961799397074</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-20.7097298134963</v>
+        <v>-20.69687521483023</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-21.10917003249411</v>
+        <v>-21.0962138218886</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-20.98451662858916</v>
+        <v>-20.97158360430233</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-29.84146038514979</v>
+        <v>-29.82839640175915</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-21.23508893858188</v>
+        <v>-21.22208334116168</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-13.00604664243915</v>
+        <v>-12.9930095398995</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.166196819925339</v>
+        <v>3.179358587742243</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.216997040393821</v>
+        <v>-5.20381692495743</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-14.39274570213706</v>
+        <v>-14.37935790111621</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.273890669784315</v>
+        <v>-6.260444855928441</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-14.5702291537507</v>
+        <v>-14.55678553768406</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-14.99393003178147</v>
+        <v>-14.98037838077522</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-14.74788575075415</v>
+        <v>-14.75831538645988</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.07143</t>
+          <t>X ≈ -0.07142</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>31</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.552852598419562</v>
+        <v>5.565337192007171</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.7317963510100256</v>
+        <v>0.7446663148603889</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.554601963510585</v>
+        <v>3.567574479419022</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.467626266522565</v>
+        <v>0.4805721066048463</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>9.586406985163464</v>
+        <v>9.599492541431523</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.2276875364609623</v>
+        <v>0.2407033905718592</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.363314214934292</v>
+        <v>3.376358133057067</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.544187158835307</v>
+        <v>-3.531028112800001</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3842760677852013</v>
+        <v>-0.3710946534209469</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.456321961714806</v>
+        <v>-4.442931889775657</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.438769599007799</v>
+        <v>-1.425323009856584</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.404711903229476</v>
+        <v>-1.391266745489112</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.399848300913021</v>
+        <v>1.413400924884478</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.875770163219094</v>
+        <v>4.865340527522406</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.06475</t>
+          <t>X ≈ -0.06474</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.379110907978088</v>
+        <v>2.331289839922746</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>18.13928316536084</v>
+        <v>17.70793343913337</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>22.72862284698056</v>
+        <v>22.17922571643252</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>20.37623885372142</v>
+        <v>19.88461716066301</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>19.81584818274399</v>
+        <v>19.33879970608753</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>15.13493921671741</v>
+        <v>14.7758810454639</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>10.0572515157405</v>
+        <v>9.822801352553441</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>14.55992667812807</v>
+        <v>14.21706299913713</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>12.00380513224773</v>
+        <v>11.72277555105907</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>8.618872780581498</v>
+        <v>8.419980848208624</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>10.91497322678124</v>
+        <v>10.65486869106597</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.953975848712531</v>
+        <v>5.81605309651011</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>14.42371822823726</v>
+        <v>12.70376606705129</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>4.550627702974808</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>59</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.34985226104591</v>
+        <v>3.361901448774063</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>8.453107437399559</v>
+        <v>8.464256081918734</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>8.055944966651488</v>
+        <v>8.067231731928679</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2695265049266453</v>
+        <v>-0.2561240266370604</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.944459499810826</v>
+        <v>5.956414733546822</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9.634380487297918</v>
+        <v>9.645363410710488</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7.854742206358281</v>
+        <v>7.866217470798667</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>10.76034532825084</v>
+        <v>10.77120993889552</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.617365755511692</v>
+        <v>5.629567708105697</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>9.825514297900597</v>
+        <v>9.836844624727064</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.790012363691552</v>
+        <v>2.855415435282559</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>11.55259103073553</v>
+        <v>10.61750882670625</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.047590657078771</v>
+        <v>6.061146703430374</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.907481480881259</v>
+        <v>2.897051845183107</v>
       </c>
     </row>
     <row r="14">
@@ -991,150 +991,150 @@
         <v>52</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-7.331071754930157</v>
+        <v>-7.316458516096795</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-10.89107040151342</v>
+        <v>-10.87514806867864</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-18.97152215480639</v>
+        <v>-18.95346106887791</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-16.92575873222405</v>
+        <v>-16.90821541874258</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.950707184009204</v>
+        <v>-5.935897969865557</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1135398284840221</v>
+        <v>0.1267331567167176</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.817904256603207</v>
+        <v>-3.803644319390983</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-11.98536624976658</v>
+        <v>-11.96885529328789</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-12.05168277429804</v>
+        <v>-12.03511704553989</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-21.45826435640009</v>
+        <v>-22.51812401023906</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-19.73994075763989</v>
+        <v>-19.72648346392967</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-15.8594037541406</v>
+        <v>-15.84595146542049</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-16.2796583650855</v>
+        <v>-16.2661023187339</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-14.10686010973317</v>
+        <v>-14.11728974543132</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.0447</t>
+          <t>X ≈ -0.04469</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>82</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.959080022395831</v>
+        <v>2.970936468615918</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.766508815509603</v>
+        <v>3.778542993900416</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.369967874723841</v>
+        <v>3.382170052039591</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4.719522672863185</v>
+        <v>4.731372961658977</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.178665773973201</v>
+        <v>4.190739685746784</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.480476546920379</v>
+        <v>4.492411685469229</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.4820809969614288</v>
+        <v>-0.4687677624422903</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.615046174624069</v>
+        <v>-4.600480094999014</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.8740371888538476</v>
+        <v>0.2139304714602943</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.462936394070368</v>
+        <v>2.476341521723199</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.038670874630839</v>
+        <v>1.052128168341056</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1464581631462281</v>
+        <v>-0.133005874426118</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.005737164335031</v>
+        <v>-2.992181117983428</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.536503636936239</v>
+        <v>-1.546933272634391</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.03802</t>
+          <t>X ≈ -0.03801</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>123</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.411537730390705</v>
+        <v>-5.397125488615018</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-13.57561993417646</v>
+        <v>-13.55856437518877</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-7.480086138454091</v>
+        <v>-7.464642099443836</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-4.911524785673137</v>
+        <v>-4.896786138720103</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5.017733427384954</v>
+        <v>-5.447216784623755</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-5.898717216862117</v>
+        <v>-6.32612561237422</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.106121734205189</v>
+        <v>-3.536121050532593</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.316995445288867</v>
+        <v>-2.752527389576777</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.191003461552654</v>
+        <v>-3.177804722597891</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.415112386418173</v>
+        <v>-2.401707258765342</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.619865710735937</v>
+        <v>-2.606408417025719</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.1464581631462281</v>
+        <v>-0.133005874426118</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.005737164334668</v>
+        <v>-2.992181117983066</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.122032948428689</v>
+        <v>2.111603312730537</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>140</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.380603731273673</v>
+        <v>1.018219597314094</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.546375754537117</v>
+        <v>1.171014402241944</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.6030617966267116</v>
+        <v>-0.9787360761650348</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.08391322144887425</v>
+        <v>-0.4588464694402106</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.663379849193404</v>
+        <v>3.676490653568344</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.039178213090942</v>
+        <v>-1.026135316796577</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.12391193036337</v>
+        <v>-1.110845676062894</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.019666757716799</v>
+        <v>-3.006485748421561</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.9378095010417837</v>
+        <v>-0.9246107620870205</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-5.359363257497961</v>
+        <v>-5.34595812984513</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-5.564116581815711</v>
+        <v>-5.550659288105493</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-7.378559463986932</v>
+        <v>-7.365003417635329</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-5.700266703138894</v>
+        <v>-5.710696338837046</v>
       </c>
     </row>
     <row r="18">
@@ -1199,306 +1199,306 @@
         <v>208</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.897284474056235</v>
+        <v>-4.884762184380612</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.538342178232362</v>
+        <v>-3.52533504681476</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.369627507163436</v>
+        <v>-4.356648364764972</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.946510260697032</v>
+        <v>-3.933399456322093</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-7.014452938366091</v>
+        <v>-7.001410042071726</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-8.060725117176723</v>
+        <v>-8.047658862876247</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-8.527908515958224</v>
+        <v>-8.514727506662986</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-10.51198532521723</v>
+        <v>-10.49878658626247</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-9.439033587168346</v>
+        <v>-9.425628459515515</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.355325373024492</v>
+        <v>-4.341868079314274</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-5.763249907986761</v>
+        <v>-5.749797619266651</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.260427595854736</v>
+        <v>-4.246871549503133</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.453013955886142</v>
+        <v>-5.463443591584294</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.01797</t>
+          <t>X ≈ -0.01796</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>246</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.306446450291183</v>
+        <v>-3.29392416061556</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.292003803092925</v>
+        <v>-3.279093993516874</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-5.312888769852123</v>
+        <v>-5.29988163843452</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.337107181960064</v>
+        <v>-2.3241280395616</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.688536527113627</v>
+        <v>-3.675425722738687</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.578086459316488</v>
+        <v>-2.565043563022122</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.882332371710902</v>
+        <v>-3.869266117410426</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2844751200856237</v>
+        <v>-0.2712941107903859</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.15848313634941</v>
+        <v>-1.145284397394647</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3825920612148224</v>
+        <v>-0.3691869335619913</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.40035351561361</v>
+        <v>-1.386896221903392</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.21149881355273</v>
+        <v>-4.19804652483262</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.444761554578939</v>
+        <v>-5.431205508227336</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-5.195040222302652</v>
+        <v>-5.205469858000804</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.01129</t>
+          <t>X ≈ -0.01128</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>280</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.493438320209897</v>
+        <v>-2.480916030534274</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.462154790317086</v>
+        <v>-4.449244980741035</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.21416635405653</v>
+        <v>-5.201159222638928</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.012484650020468</v>
+        <v>-3.999505507622004</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.408048722235492</v>
+        <v>-2.394937917860553</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.03225035833722956</v>
+        <v>0.04529325463159495</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.7667690732206864</v>
+        <v>-0.7537028189202104</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.019666757716465</v>
+        <v>-3.006485748421227</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.294952358184567</v>
+        <v>-1.281753619229804</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3593632574981243</v>
+        <v>-0.3459581298452932</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.5641165818156253</v>
+        <v>-0.5506592881054075</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.1845522898153646</v>
+        <v>0.1980045785354747</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.264297678870541</v>
+        <v>2.277853725222144</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.085447582575391</v>
+        <v>1.075017946877239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.004601</t>
+          <t>X ≈ -0.004598</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>352</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-8.175256502028226</v>
+        <v>-8.162734212352603</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-3.820921024083326</v>
+        <v>-3.808011214507275</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.227153367043549</v>
+        <v>-2.214146235625947</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.08553659807248</v>
+        <v>-4.072557455674016</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-5.760321449508218</v>
+        <v>-5.747210645133279</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.178788602701715</v>
+        <v>-5.16574570640735</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-7.25215868361029</v>
+        <v>-7.239092429309814</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.605705718755559</v>
+        <v>-2.592524709460321</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.371251059483249</v>
+        <v>-4.358052320528486</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-6.073648971783904</v>
+        <v>-6.060243844131072</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-6.278402296101483</v>
+        <v>-6.264945002391265</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-4.539473684210471</v>
+        <v>-4.526021395490361</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.255182840609983</v>
+        <v>-3.24162679425838</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.005461508333696</v>
+        <v>-3.015891144031848</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.002082</t>
+          <t>X ≈ 0.002084</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>343</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>4.066328443638419</v>
+        <v>4.078850733314042</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4139385041434807</v>
+        <v>0.4268483137195318</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.438656149974904</v>
+        <v>-1.425649018557301</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.474583775384765</v>
+        <v>-2.461604632986301</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.09755309541333901</v>
+        <v>-0.08444229103839973</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.6747467262107918</v>
+        <v>-0.6617038299164264</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1151551250300429</v>
+        <v>0.1282213793305189</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3520282737513938</v>
+        <v>-0.338847264456156</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.919333356101298</v>
+        <v>1.932532095056061</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.156000036260096</v>
+        <v>1.169457329970314</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.02420243558803747</v>
+        <v>0.03765472430814754</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.145323312383105</v>
+        <v>-2.131767266031503</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.02096641159369</v>
+        <v>-1.031396047291842</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.008766</t>
+          <t>X ≈ 0.008767</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>278</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.054589399346661</v>
+        <v>-1.042067109671038</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.306450782094977</v>
+        <v>-2.293540972518926</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.262470567828338</v>
+        <v>-1.249463436410736</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.571066356084188</v>
+        <v>-2.558087213685724</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.908048722235449</v>
+        <v>-4.89493791786051</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.330031244951321</v>
+        <v>-5.316988348656956</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-3.975916041360534</v>
+        <v>-3.962849787060058</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.522236130789516</v>
+        <v>-5.509055121494278</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.662372707619305</v>
+        <v>-6.649173968664542</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.994512281136274</v>
+        <v>-4.981107153483443</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-5.918690065885592</v>
+        <v>-5.905232772175374</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.1648824481085</v>
+        <v>-5.15143015938839</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.146288138190101</v>
+        <v>-4.132732091838498</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.53685457569798</v>
+        <v>-3.547284211396132</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>312</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.172925499697158</v>
+        <v>-2.160403210021535</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.305244477082141</v>
+        <v>2.318154286658192</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.589862949972733</v>
+        <v>1.602870081390336</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.2029608404967291</v>
+        <v>-0.1899816980982649</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.7413820555688631</v>
+        <v>-0.7282712511939238</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.1970855231724045</v>
+        <v>0.2101284194667699</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.4328646264131208</v>
+        <v>0.4459308807135969</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.9958572339068681</v>
+        <v>-0.9826762246116303</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.979934043166097</v>
+        <v>-2.966735304211333</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.150572048706955</v>
+        <v>-4.137166921054124</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.71429973199885</v>
+        <v>-3.700842438288632</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.679916574653419</v>
+        <v>-3.666464285933309</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-5.061709647136745</v>
+        <v>-5.048153600785142</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-7.055578058450237</v>
+        <v>-7.066007694148389</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>321</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.581328034930209</v>
+        <v>3.593850324605832</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.969754421965952</v>
+        <v>1.982664231542003</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.01725331661546647</v>
+        <v>0.0302604480330686</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.1640200305278157</v>
+        <v>-0.1510408881293515</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.01396772535076</v>
+        <v>-1.000856920975821</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.7165257876350992</v>
+        <v>-0.7034828913407338</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.1782065454058568</v>
+        <v>-0.1651402911053808</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.268442903688879</v>
+        <v>-1.255261894393641</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.32944278987118</v>
+        <v>-1.316244050916417</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.6219355761451695</v>
+        <v>-0.6085304484923384</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.384321299216687</v>
+        <v>-2.370864005506469</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.972991101372813</v>
+        <v>-2.959538812652703</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.081719232566975</v>
+        <v>-3.068163186215372</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.897418461038313</v>
+        <v>-1.907848096736465</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>229</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.965076963632818</v>
+        <v>2.977599253308441</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.846953132327954</v>
+        <v>4.859862941904005</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.888765648438735</v>
+        <v>4.901772779856337</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.962250222094319</v>
+        <v>1.975229364492783</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.043916343266694</v>
+        <v>4.057027147641634</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.778039503689783</v>
+        <v>4.791082399984148</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.876711899954572</v>
+        <v>6.889778154255048</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.15625339200286</v>
+        <v>8.169434401298098</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>10.27865961935762</v>
+        <v>10.29185835831238</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.991853211622271</v>
+        <v>9.005258339275102</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7.91373744188985</v>
+        <v>7.927194735600068</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.384801821942702</v>
+        <v>8.398254110662812</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.527865988290323</v>
+        <v>7.541422034641926</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.340906097859246</v>
+        <v>7.330476462161094</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>181</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.650208088629775</v>
+        <v>1.662730378305397</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.353551602737369</v>
+        <v>3.36646141231342</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.406196708295539</v>
+        <v>2.419203839713141</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.088936028748279</v>
+        <v>3.101915171146743</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.760459565057332</v>
+        <v>4.773570369432271</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.505415314927689</v>
+        <v>4.518458211222054</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.868195409810127</v>
+        <v>3.881261664110603</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.848525823183238</v>
+        <v>2.861706832478475</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.34001212484629</v>
+        <v>3.353210863801053</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.594859315508948</v>
+        <v>3.608264443161779</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.285133615500783</v>
+        <v>2.298590909211001</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.767030585000917</v>
+        <v>1.780482873721027</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.8631687773251429</v>
+        <v>-0.84961273097354</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.6134474450489407</v>
+        <v>-0.6238770807470928</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>154</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6.597470770699154</v>
+        <v>6.609993060374777</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.388494560332262</v>
+        <v>2.401404369908313</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.721281583745771</v>
+        <v>4.734260726144235</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.130912316725542</v>
+        <v>6.144023121100481</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>9.675107501194461</v>
+        <v>9.688150397488826</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>12.18777638132482</v>
+        <v>12.20084263562529</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>10.42189168384201</v>
+        <v>10.43507269313725</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>11.01024244701032</v>
+        <v>11.02344118596508</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.562714664579829</v>
+        <v>7.57611979223266</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.059260041560918</v>
+        <v>6.072717335271136</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.145591250854409</v>
+        <v>4.159043539574519</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.322739237312135</v>
+        <v>6.336295283663738</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.975057972185823</v>
+        <v>3.964628336487671</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>141</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.848048249288027</v>
+        <v>-2.835525959612404</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2043027133160749</v>
+        <v>-0.1913929037400237</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.726830994380755</v>
+        <v>-2.713823862963153</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.178138145461197</v>
+        <v>-1.165159003062733</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.134999076845382</v>
+        <v>-3.121888272470443</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.128337280973732</v>
+        <v>-2.115294384679366</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.0854114237779271</v>
+        <v>-0.07234516947745107</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.284284610064695</v>
+        <v>2.297465619359933</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.769384014662528</v>
+        <v>5.782582753617291</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>11.30223755303885</v>
+        <v>11.31564268069168</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>11.8067040868773</v>
+        <v>11.82016138058752</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>13.2595269605348</v>
+        <v>13.27297924925491</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>14.25771206590195</v>
+        <v>14.27126811225355</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>13.7982135400222</v>
+        <v>13.78778390432405</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>104</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>9.045023218251622</v>
+        <v>9.057545507927244</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>9.356526528364206</v>
+        <v>9.369436337940257</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>10.88473474484456</v>
+        <v>10.89774187626217</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>11.01498787745206</v>
+        <v>11.02796701985053</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>11.43810512391829</v>
+        <v>11.45121592829323</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>13.65862398471094</v>
+        <v>13.67166688100531</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.76619795974635</v>
+        <v>8.779264214046826</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.375937637887873</v>
+        <v>6.389118647183111</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.468783905551774</v>
+        <v>2.481982644506537</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.464812566677701</v>
+        <v>5.478217694330532</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.260059242360121</v>
+        <v>5.273516536070339</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.06367316893632</v>
+        <v>11.07712545765643</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>18.33572625029905</v>
+        <v>18.34928229665066</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>19.54698604411385</v>
+        <v>19.5365564084157</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>97</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.269448277728138</v>
+        <v>6.281970567403761</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>9.812513840021637</v>
+        <v>9.825423649597688</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>14.57228430868278</v>
+        <v>14.58529144010038</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>17.79532094644492</v>
+        <v>17.80830008884339</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>14.16411622621808</v>
+        <v>14.17722703059302</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>15.49248599898532</v>
+        <v>15.50552889527968</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16.43868011676459</v>
+        <v>16.45174637106507</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>18.03335238808618</v>
+        <v>18.04653339738142</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>12.81771332664618</v>
+        <v>12.83091206560094</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.99851597666976</v>
+        <v>13.0119211043226</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.82469048740373</v>
+        <v>13.83814778111395</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>14.89000147980072</v>
+        <v>14.90345376852083</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>13.43881903380426</v>
+        <v>13.45237508015586</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.68854036608055</v>
+        <v>13.67811073038239</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>57</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.892526592070773</v>
+        <v>1.905048881746396</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.227818950718046</v>
+        <v>-3.214909141141995</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.640470237422157</v>
+        <v>1.653477368839759</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.525109334941966</v>
+        <v>3.53808847734043</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2.986688119869818</v>
+        <v>2.999798924244757</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-3.733413802063687</v>
+        <v>-3.720370905769322</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-2.063761554423692</v>
+        <v>-2.050695300123216</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.240984871356218</v>
+        <v>6.254165880651456</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.8375588744752633</v>
+        <v>-0.8243601355205001</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.821087870321449</v>
+        <v>1.83449299797428</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.61633454600387</v>
+        <v>1.629791839714088</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.159489633173841</v>
+        <v>5.172941921893951</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.75677888187806</v>
+        <v>11.77033492822966</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.2521142492421</v>
+        <v>10.24168461354395</v>
       </c>
     </row>
     <row r="33">
@@ -1979,98 +1979,98 @@
         <v>65</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9.045023218251586</v>
+        <v>9.057545507927209</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.433449605287308</v>
+        <v>7.446359414863359</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.51312649164678</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>11.78421864668282</v>
+        <v>11.79719778908129</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.168874354687581</v>
+        <v>8.181985159062521</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.7740086000955557</v>
+        <v>0.7870514963899211</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.6892748828232982</v>
+        <v>0.7023411371237742</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.299014560964856</v>
+        <v>3.312195570260094</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>7.853399290167161</v>
+        <v>7.866598029121924</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.541735643600759</v>
+        <v>8.555140771253591</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.336982319283152</v>
+        <v>8.35043961299337</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5.294442399705552</v>
+        <v>5.307894688425662</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.349282296650713</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.5085245056522965</v>
+        <v>0.4980948699541443</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.08228</t>
+          <t>X ≈ 0.08227</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>40</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.506561679789982</v>
+        <v>2.519083969465605</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>18.39498806682577</v>
+        <v>18.40789787640182</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>15.50011936022918</v>
+        <v>15.51312649164678</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>18.13037249283666</v>
+        <v>18.14335163523513</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>12.59195127776449</v>
+        <v>12.60506208213943</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.38939321548019</v>
+        <v>5.402436111774556</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12.80465949820785</v>
+        <v>12.81772575250832</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.3374760994264</v>
+        <v>12.35065710872164</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>12.27647621324409</v>
+        <v>12.28967495219885</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.42635102821616</v>
+        <v>6.439756155868992</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.721597703898595</v>
+        <v>8.735054997608813</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.755980861244012</v>
+        <v>3.769433149964122</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>8.335726250299111</v>
+        <v>8.349282296650713</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.585447582575412</v>
+        <v>8.57501794687726</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MACD-12-26 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MACD-12-26 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.00230066201549306</v>
+        <v>0.002044047362439017</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.01343862581914124</v>
+        <v>-0.01369939654680508</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.02972229628726808</v>
+        <v>-0.02998115569857163</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1298614252919776</v>
+        <v>-0.1300953805992009</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1188700724670255</v>
+        <v>-0.1191094578215655</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.07623330816683449</v>
+        <v>-0.07648175320230877</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1476692021090997</v>
+        <v>-0.1479007711386373</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01618243715897449</v>
+        <v>-0.01644847528226734</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.03933252059344028</v>
+        <v>-0.0395933404840747</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.09512286148613214</v>
+        <v>-0.09537436376994179</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1397642682761813</v>
+        <v>-0.1400060077596805</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2381597637559878</v>
+        <v>-0.2383774431527925</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2295973150244563</v>
+        <v>-0.2298192658492866</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1859251580205949</v>
+        <v>-0.1856658138065157</v>
       </c>
     </row>
     <row r="7">
@@ -2266,153 +2266,153 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4088</v>
+        <v>4089</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.005952072377198192</v>
+        <v>0.005675875852773515</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.00745095756447256</v>
+        <v>-0.007732457663038872</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.0231790052258134</v>
+        <v>-0.02345887420687376</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1480560088714711</v>
+        <v>-0.1483048663506139</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1606725933607009</v>
+        <v>-0.1609213244003271</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1184192845198311</v>
+        <v>-0.1186768977446278</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.1898459962976062</v>
+        <v>-0.1900867474916339</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.05749214678758108</v>
+        <v>-0.05776779970327794</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.08059683830734343</v>
+        <v>-0.0808673047625561</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1352325494964575</v>
+        <v>-0.1354942716902485</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2040928363116379</v>
+        <v>-0.2043389417851458</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.253799089856237</v>
+        <v>-0.2540329952326559</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.2690670977077332</v>
+        <v>-0.2692996104397452</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.250168855780764</v>
+        <v>-0.24987811572975</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.09482</t>
+          <t>X &gt; -0.09481</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4071</v>
+        <v>4072</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.04485849650771456</v>
+        <v>-0.04517551645846396</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.07611161478089912</v>
+        <v>-0.07643121272649012</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.139273094449905</v>
+        <v>-0.1395798517281932</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1672261349506314</v>
+        <v>-0.1675253858329668</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2021663692943108</v>
+        <v>-0.202460583873787</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.160986779616664</v>
+        <v>-0.1612893784215501</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2568902810956857</v>
+        <v>-0.2571700552876592</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1220529660629452</v>
+        <v>-0.1223688844122606</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.07141387507779484</v>
+        <v>-0.07174275690097431</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.171808480986293</v>
+        <v>-0.1721182307845908</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3137483933031859</v>
+        <v>-0.3140247569924313</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.3638325441083055</v>
+        <v>-0.3640965505758871</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.303762944199903</v>
+        <v>-0.3040444895019974</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2858371140593405</v>
+        <v>-0.2854928586237406</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.08814</t>
+          <t>X &gt; -0.08813</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4052</v>
+        <v>4053</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.02111359696274206</v>
+        <v>-0.02149645355451213</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.004240035329701186</v>
+        <v>0.003838835811414754</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.08196284503787155</v>
+        <v>-0.08234594929810157</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1352602004178749</v>
+        <v>-0.1356294132512019</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1924614284654851</v>
+        <v>-0.1928207342071744</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1278481638301798</v>
+        <v>-0.1282213617541572</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-0.1502545430581321</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.03684622684271233</v>
+        <v>-0.0372463157671703</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.01031205394842516</v>
+        <v>-0.010719330699132</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1318343761230878</v>
+        <v>-0.1322182094255595</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.2734701136106636</v>
+        <v>-0.2738207420361718</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3239402043701887</v>
+        <v>-0.324278317360168</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2862821385486569</v>
+        <v>-0.2866328488845653</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2694388932390126</v>
+        <v>-0.2690481769816273</v>
       </c>
     </row>
     <row r="10">
@@ -2422,205 +2422,205 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4031</v>
+        <v>4032</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.07009509567980388</v>
+        <v>-0.0705328414119748</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.03795121300434801</v>
+        <v>0.03747255493792778</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.145600580394273</v>
+        <v>-0.146037495491484</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1751211968440956</v>
+        <v>-0.1755498986589643</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1060685242156865</v>
+        <v>-0.1065192096200107</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.04264441759732307</v>
+        <v>-0.04310844268090364</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.01480558351573791</v>
+        <v>-0.01527746611010627</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.07651498969143944</v>
+        <v>0.07601619737938137</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.02920168400721934</v>
+        <v>0.02871384246390107</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.08851886025967559</v>
+        <v>-0.08898517217858171</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2298152856899165</v>
+        <v>-0.230248595947586</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2559209488229328</v>
+        <v>-0.2563477127032101</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.2158610512881936</v>
+        <v>-0.216301635905694</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2498290237257663</v>
+        <v>-0.2493868150275205</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.07477</t>
+          <t>X &gt; -0.07476</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4019</v>
+        <v>4020</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.03808117735283645</v>
+        <v>-0.03856542304612987</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.09989999934871463</v>
+        <v>0.09936613037007191</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.08300719063931439</v>
+        <v>-0.08349965571120066</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1129881425567163</v>
+        <v>-0.1134721861048149</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.01728407476776539</v>
+        <v>-0.01779718815094355</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.02063235131330288</v>
+        <v>0.02011237791157328</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.02398388966342679</v>
+        <v>0.0234620326176298</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.06728976402266085</v>
+        <v>0.06675248875143325</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.04486587527191688</v>
+        <v>0.0443333372920236</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.04580905132647217</v>
+        <v>-0.04632734313697995</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.2117687804375734</v>
+        <v>-0.2122480100969</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2131810387808528</v>
+        <v>-0.2136598385987796</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1717364362680556</v>
+        <v>-0.1722297650254916</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2065404741551404</v>
+        <v>-0.2060765804859415</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.06809</t>
+          <t>X &gt; -0.06808</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3988</v>
+        <v>3989</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.08154129446641889</v>
+        <v>-0.08211543083420736</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.09498806682577055</v>
+        <v>0.0943512630551524</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1112834904835012</v>
+        <v>-0.1118735083532272</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1175014441318112</v>
+        <v>-0.1180887248548785</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.09193663817244158</v>
+        <v>-0.09253671726025203</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.01902284510979513</v>
+        <v>0.01839808325314607</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.001973793406627067</v>
+        <v>-0.002594567811954107</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.09536292967176507</v>
+        <v>0.09471217755766759</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.04820173290350027</v>
+        <v>0.04756178244422671</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.01152472328684695</v>
+        <v>-0.01215969687330443</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2022309104837845</v>
+        <v>-0.2028207538942084</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2039188881294223</v>
+        <v>-0.2045082181140501</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1839528672742219</v>
+        <v>-0.184552289815457</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2460469008749513</v>
+        <v>-0.2454884457023496</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.06141</t>
+          <t>X &gt; -0.0614</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3948</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1064719145519746</v>
+        <v>-0.1071786567969824</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.08783153903578267</v>
+        <v>-0.08856587707128938</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.3426908495256953</v>
+        <v>-0.3433666867261351</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3251381239479585</v>
+        <v>-0.3258169268068087</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2936365856994669</v>
+        <v>-0.294331244453069</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1341272701040523</v>
+        <v>-0.1348584520686984</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1038909697910952</v>
+        <v>-0.1046313542189949</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.05118786818493959</v>
+        <v>-0.05194850726623201</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.07292900062581964</v>
+        <v>-0.07368537168778744</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.09896542748004578</v>
+        <v>-0.09972751914999378</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.3148672239312518</v>
+        <v>-0.3155779137836063</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2663089057266035</v>
+        <v>-0.2670317778657108</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.331953587593496</v>
+        <v>-0.3183975412418931</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2848665005046414</v>
+        <v>-0.2952961362027935</v>
       </c>
     </row>
     <row r="14">
@@ -2633,150 +2633,150 @@
         <v>3889</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1589077917338315</v>
+        <v>-0.1598080541301528</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2174060825198794</v>
+        <v>-0.2183206972256784</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4701065124607595</v>
+        <v>-0.4709638342449338</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3259818075484304</v>
+        <v>-0.3268742374547955</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3882747109360523</v>
+        <v>-0.3891612811468192</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2823252535668388</v>
+        <v>-0.283234150166912</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2246313548239627</v>
+        <v>-0.2255570628011583</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.2152095854875142</v>
+        <v>-0.2161465911756011</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1592564345708212</v>
+        <v>-0.1602093962976738</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2495296609070081</v>
+        <v>-0.2504752065988782</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.3771423321003908</v>
+        <v>-0.3636850383901731</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.4456133789205552</v>
+        <v>-0.4321610902004451</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.4287376221616768</v>
+        <v>-0.4151815758100739</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3332975961337894</v>
+        <v>-0.3437272318319415</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.04804</t>
+          <t>X &gt; -0.04803</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3837</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.061708801354321</v>
+        <v>-0.06281930666539637</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.07275386865810418</v>
+        <v>-0.07389666195969369</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.219370621555889</v>
+        <v>-0.2204843304135764</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.101017408256503</v>
+        <v>-0.1021596840466614</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3128912111706654</v>
+        <v>-0.3139904946434768</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2876901178531668</v>
+        <v>-0.2887901313913019</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.175934406454779</v>
+        <v>-0.1770659141582982</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.05569742845271719</v>
+        <v>-0.0568708933622446</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.001912752206820301</v>
+        <v>0.0007223727303724559</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.03789650645437348</v>
+        <v>0.05130163410720456</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.1147327626117161</v>
+        <v>-0.1012754689014983</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.2367217710207754</v>
+        <v>-0.2232694823006653</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2139219123279403</v>
+        <v>-0.2003658659763374</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1466347734318987</v>
+        <v>-0.1570644091300508</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.04136</t>
+          <t>X &gt; -0.04135</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3755</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1276754281312904</v>
+        <v>-0.1290690998939112</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1565939592311381</v>
+        <v>-0.1580245053100384</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.2977529801963499</v>
+        <v>-0.2991574753832609</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2062861929840167</v>
+        <v>-0.2077121945520872</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4109758111125572</v>
+        <v>-0.4123627648943327</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3918151954860321</v>
+        <v>-0.3931998648087571</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1692489149976453</v>
+        <v>-0.1706958604807198</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.04386757745568559</v>
+        <v>0.04235039945645269</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.01713230872661597</v>
+        <v>-0.003933569771852774</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.01506042318197842</v>
+        <v>-0.001655295529147338</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.1399202721333808</v>
+        <v>-0.126462978423163</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2386929070649089</v>
+        <v>-0.2252406183447988</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.1529555073573476</v>
+        <v>-0.1393994610057447</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1162834427242103</v>
+        <v>-0.1267130784223625</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>3632</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.05126594388906369</v>
+        <v>0.04933699476817566</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2978499270349104</v>
+        <v>0.2957933371996191</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.05451867995800086</v>
+        <v>-0.0564937615177783</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.04694028249371485</v>
+        <v>-0.04891371020939772</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2549650217949591</v>
+        <v>-0.2418542174200198</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2053204409074922</v>
+        <v>-0.1922775446131268</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.06978984099915664</v>
+        <v>-0.05672358669868061</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.1238197117611861</v>
+        <v>0.1370007210564239</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.09035286522646402</v>
+        <v>0.1035516041812272</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.06621886962585677</v>
+        <v>0.07962399727868785</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.05593533574899823</v>
+        <v>-0.04247804203878047</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.2418164955841817</v>
+        <v>-0.2283642068640717</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.05634423428239188</v>
+        <v>-0.04278818793078898</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.1920854570721815</v>
+        <v>-0.2025150927703336</v>
       </c>
     </row>
     <row r="18">
@@ -2841,306 +2841,306 @@
         <v>3492</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.002029385502069658</v>
+        <v>0.01049290417355309</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2477944814878512</v>
+        <v>0.2607042910639024</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.0325266878807895</v>
+        <v>-0.01951955646318737</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.04545797680822972</v>
+        <v>-0.03247883440976551</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.4120578860384754</v>
+        <v>-0.3989470816635361</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1718897169367892</v>
+        <v>-0.1588468206424238</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.0275283597531697</v>
+        <v>-0.01446210545269366</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.2498472334470137</v>
+        <v>0.2630282427422515</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1315735786507375</v>
+        <v>0.1447723176055007</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2837393443673619</v>
+        <v>0.297144472020193</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1648966729707482</v>
+        <v>0.1783539666809659</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.001178359832735509</v>
+        <v>0.01227392888737455</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.2372153682830742</v>
+        <v>0.2507714146346771</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.0287465516475649</v>
+        <v>0.01831691594941276</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.02131</t>
+          <t>X &gt; -0.0213</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>3284</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3080233119459379</v>
+        <v>0.3205456016215606</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.523489893865964</v>
+        <v>0.5363997034420152</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.1895225270988448</v>
+        <v>0.2025296585164469</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2284236499621386</v>
+        <v>0.2414027923606028</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.1881948854510895</v>
+        <v>-0.1750840810761503</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.2615004018382692</v>
+        <v>0.2745432981326346</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4812733837133649</v>
+        <v>0.494339638013841</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.8058074027150681</v>
+        <v>0.8189884120103059</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8057088563622301</v>
+        <v>0.8189075953169933</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8995544386911831</v>
+        <v>0.9129595663440142</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.4511957550557071</v>
+        <v>0.4646530487659248</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.3637762327421825</v>
+        <v>0.3772285214622926</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5220843501773089</v>
+        <v>0.5356403965289118</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.3759469735620016</v>
+        <v>0.3655173378638494</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.01463</t>
+          <t>X &gt; -0.01462</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>3038</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6007025619493405</v>
+        <v>0.6132248516249632</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.8324469213353112</v>
+        <v>0.8453567309113623</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6350765689191036</v>
+        <v>0.6480837003367057</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.43616577789264</v>
+        <v>0.4491449202911042</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.09524291700084575</v>
+        <v>0.108353721375785</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4914340318066905</v>
+        <v>0.5044769281010559</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8346134152585805</v>
+        <v>0.8476796695590565</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.8940922942914256</v>
+        <v>0.9072733035866634</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.9647579775627122</v>
+        <v>0.9779567165174754</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.003375386346505</v>
+        <v>1.016780513999336</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.6011237078485436</v>
+        <v>0.6145810015587614</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.7342560422841728</v>
+        <v>0.7477083310042829</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.005245670970602</v>
+        <v>1.018801717322205</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.827053902522735</v>
+        <v>0.8166242668245829</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.007942</t>
+          <t>X &gt; -0.00794</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2758</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.914828539833529</v>
+        <v>0.9273508295091517</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.369969937746724</v>
+        <v>1.382879747322775</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.228908337749118</v>
+        <v>1.24191546916672</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.8878054152442232</v>
+        <v>0.9007845576426874</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.3493842001720537</v>
+        <v>0.362495004546993</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.538051663631002</v>
+        <v>0.5510945599253674</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.9971903176422643</v>
+        <v>1.01025657194274</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.291428238657709</v>
+        <v>1.304609247952946</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.194170194389841</v>
+        <v>1.207368933344604</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.141724487244446</v>
+        <v>1.155129614897277</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7194222144134415</v>
+        <v>0.7328795081236592</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.7900635298444527</v>
+        <v>0.8035158185645628</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.877423132097519</v>
+        <v>0.8909791784491219</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.8008210416036832</v>
+        <v>0.790391405905531</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; -0.00126</t>
+          <t>X &gt; -0.001257</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2406</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.24471629325636</v>
+        <v>2.257238582931983</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.129402031913052</v>
+        <v>2.142311841489104</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.734533325316463</v>
+        <v>1.747540456734065</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.615409899320476</v>
+        <v>1.62838904171894</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.243239723317288</v>
+        <v>1.256350527692227</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.374430621963967</v>
+        <v>1.387473518258332</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.204077619571144</v>
+        <v>2.21714387387162</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.861582500091401</v>
+        <v>1.874763509386639</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.008396412745341</v>
+        <v>2.021595151700105</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.197340221898628</v>
+        <v>2.210745349551459</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.743210338977548</v>
+        <v>1.756667632687765</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.569779697486737</v>
+        <v>1.583231986206847</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.48202716467982</v>
+        <v>1.495583211031423</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.357683659050878</v>
+        <v>1.347254023352725</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.005423</t>
+          <t>X &gt; 0.005425</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2063</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.94185009471974</v>
+        <v>1.954372384395363</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.414619671285301</v>
+        <v>2.427529480861352</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.262116451843333</v>
+        <v>2.275123583260935</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.295423389588976</v>
+        <v>2.30840253198744</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.466163589931256</v>
+        <v>1.479274394306195</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.715132430215995</v>
+        <v>1.72817532651036</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.551387564131304</v>
+        <v>2.56445381843178</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.229623457642582</v>
+        <v>2.24280446693782</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.023204279167501</v>
+        <v>2.036403018122265</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.384906529912726</v>
+        <v>2.398311657565557</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.840841523578661</v>
+        <v>1.854298817288878</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.826751583493163</v>
+        <v>1.840203872213273</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.085120336581227</v>
+        <v>2.09867638293283</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.753164499686399</v>
+        <v>1.742734863988247</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1785</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.408522464103754</v>
+        <v>2.421044753779377</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.149890027610077</v>
+        <v>3.162799837186128</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.811043729977072</v>
+        <v>2.824050861394674</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.053341680511743</v>
+        <v>3.066320822910207</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.458898056475988</v>
+        <v>2.472008860850927</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.812362403155234</v>
+        <v>2.825405299449599</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.567964820336748</v>
+        <v>3.581031074637224</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.436915875336759</v>
+        <v>3.450096884631996</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.375915989154457</v>
+        <v>3.38911472810922</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.534194165471064</v>
+        <v>3.547599293123895</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.049328796335558</v>
+        <v>3.062786090045776</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.915644726790234</v>
+        <v>2.929097015510344</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.055614205481184</v>
+        <v>3.069170251832787</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.577044221230864</v>
+        <v>2.566614585532712</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1473</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.378930994114533</v>
+        <v>3.391453283790156</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.328796620797256</v>
+        <v>3.341706430373307</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.069705239387361</v>
+        <v>3.082712370804963</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.743067672741638</v>
+        <v>3.756046815140103</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.136757795076115</v>
+        <v>3.149868599451054</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.366311070198428</v>
+        <v>3.379353966492793</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.232018629233004</v>
+        <v>4.24508488353348</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.375833193791635</v>
+        <v>4.389014203086873</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.72216528316941</v>
+        <v>4.735364022124173</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.16192468741508</v>
+        <v>5.175329815067911</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.48195072494407</v>
+        <v>4.495408018654288</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.31266789450946</v>
+        <v>4.32612018322957</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.774965897278058</v>
+        <v>4.788521943629661</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.617355253994269</v>
+        <v>4.606925618296117</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1152</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.322533902012246</v>
+        <v>3.335056191687869</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.707488066825768</v>
+        <v>3.720397876401819</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.920258249118064</v>
+        <v>3.933265380535666</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.831761381725563</v>
+        <v>4.844740524124028</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.293340166653394</v>
+        <v>4.306450971028333</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.503976548813505</v>
+        <v>4.51701944510787</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.46090949820789</v>
+        <v>5.473975752508366</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.948587210537504</v>
+        <v>5.961768219832742</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.408420657688531</v>
+        <v>6.421619396643294</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.773573250438382</v>
+        <v>6.786978378091213</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.395208815009696</v>
+        <v>6.408666108719913</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.342786416799569</v>
+        <v>6.356238705519679</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.964198472521332</v>
+        <v>6.977754518872935</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.432669804797619</v>
+        <v>6.422240169099467</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>923</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.411220401350157</v>
+        <v>3.42374269102578</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.42478221633823</v>
+        <v>3.437692025914281</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.679967680922573</v>
+        <v>3.692974812340175</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.543698603345888</v>
+        <v>5.556677745744352</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.355223217092785</v>
+        <v>4.368334021467724</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.435980431081468</v>
+        <v>4.449023327375834</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.109643246853615</v>
+        <v>5.122709501154091</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.400856381116526</v>
+        <v>5.414037390411764</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.448198856797717</v>
+        <v>5.46139759575248</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.223209099722119</v>
+        <v>6.23661422737495</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>6.01845577540454</v>
+        <v>6.031913069114758</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.836154209022993</v>
+        <v>5.849606497743103</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.824350302303451</v>
+        <v>6.837906348655054</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.20733273967182</v>
+        <v>6.196903103973668</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>742</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.840793485719949</v>
+        <v>3.853315775395572</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.442157878146524</v>
+        <v>3.455067687722575</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.990685397965024</v>
+        <v>4.003692529382626</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6.142501872890584</v>
+        <v>6.155481015289048</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.256371762939715</v>
+        <v>4.269482567314654</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.4190428111675</v>
+        <v>4.432085707461866</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.412476209798193</v>
+        <v>5.425542464098669</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.023459926919649</v>
+        <v>6.036640936214887</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.962460040737348</v>
+        <v>5.975658779692111</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.864356419051745</v>
+        <v>6.877761546704576</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.929144873709902</v>
+        <v>6.942602167420119</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.828757141567465</v>
+        <v>6.842209430287575</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.699607651916359</v>
+        <v>8.713163698267962</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>7.87116186828969</v>
+        <v>7.860732232591538</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>588</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.118806577749211</v>
+        <v>3.131328867424834</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.718117318526446</v>
+        <v>3.731027128102497</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.343656775195164</v>
+        <v>4.356663906612766</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.514726234333274</v>
+        <v>6.527705376731738</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.765420665519613</v>
+        <v>3.778531469894553</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.042454439969966</v>
+        <v>3.055497336264331</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.637992831541226</v>
+        <v>3.651059085841702</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.871489704868559</v>
+        <v>4.884670714163796</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.640421791475383</v>
+        <v>4.653620530430146</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>6.681453069032486</v>
+        <v>6.694858196685317</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.156971853558446</v>
+        <v>7.170429147268663</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.531491065325646</v>
+        <v>7.544943354045756</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.322120808122229</v>
+        <v>9.335676854473832</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.891570031554991</v>
+        <v>8.881140395856839</v>
       </c>
     </row>
     <row r="30">
@@ -3465,98 +3465,98 @@
         <v>447</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.000968838626719</v>
+        <v>5.013491128302341</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.95539075138953</v>
+        <v>4.968300560965581</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.573944863584885</v>
+        <v>6.586951995002487</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8.941334461516767</v>
+        <v>8.954313603915232</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.942063134587769</v>
+        <v>5.955173938962709</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.673509546576362</v>
+        <v>4.686552442870727</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.812489475836522</v>
+        <v>4.825555730136998</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.687587956249651</v>
+        <v>5.700768965544889</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.284306190872719</v>
+        <v>4.297504929827483</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.223890178104305</v>
+        <v>5.237295305757137</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.690277793384041</v>
+        <v>5.703735087094259</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.724660950729472</v>
+        <v>5.738113239449582</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.765256451641385</v>
+        <v>7.778812497992988</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.343836844320364</v>
+        <v>7.333407208622212</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.05889</t>
+          <t>X &gt; 0.05888</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>343</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.77478325413405</v>
+        <v>3.787305543809673</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.620935588691665</v>
+        <v>3.633845398267717</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.266883208625678</v>
+        <v>5.279890340043281</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.312588236276909</v>
+        <v>8.325567378675373</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.275624747152264</v>
+        <v>4.288735551527203</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.949159979328563</v>
+        <v>1.962202875622928</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.613697399082525</v>
+        <v>3.626763653383001</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.478875516336011</v>
+        <v>5.492056525631249</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.834785251144957</v>
+        <v>4.847983990099721</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.150840824134526</v>
+        <v>5.164245951787358</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.820723068330068</v>
+        <v>5.834180362040286</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.105835088649265</v>
+        <v>4.119287377369375</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.560216046217477</v>
+        <v>4.573772092569079</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.643756620476267</v>
+        <v>3.633326984778115</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>246</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.791114525318484</v>
+        <v>2.803636814994107</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.179540912354227</v>
+        <v>1.192450721930278</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.597680335838938</v>
+        <v>1.61068746725654</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.573461923730989</v>
+        <v>4.586441066129453</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.3765041232929676</v>
+        <v>0.3896149276679068</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-3.391094589397881</v>
+        <v>-3.378051693103515</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.443307981466909</v>
+        <v>-1.430241727166432</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.5285330099954919</v>
+        <v>0.5417140192907297</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.687045318935141</v>
+        <v>1.700244057889904</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.056432329029171</v>
+        <v>2.069837456682002</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.664687134792892</v>
+        <v>2.67814442850311</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.1464581631462281</v>
+        <v>-0.133005874426118</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.059303486071471</v>
+        <v>1.072859532423074</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.3169914418148423</v>
+        <v>-0.3274210775129944</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>189</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.074639525021205</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.508744680582382</v>
+        <v>2.521654490158433</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.58477544488526</v>
+        <v>1.597782576302862</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.88963175209593</v>
+        <v>4.902610894494394</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4106942248809915</v>
+        <v>-0.3975834205060522</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-3.287855461768508</v>
+        <v>-3.274812565474143</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.256187062638666</v>
+        <v>-1.24312080833819</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.194269932319642</v>
+        <v>-1.181088923024404</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.448433885201759</v>
+        <v>2.461632624156522</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.127409229274356</v>
+        <v>2.140814356927187</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.980856963157834</v>
+        <v>2.994314256868051</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.746664641401487</v>
+        <v>-1.733212352681377</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.166919252346389</v>
+        <v>-2.153363205994786</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.504499507371698</v>
+        <v>-3.51492914306985</v>
       </c>
     </row>
     <row r="34">
@@ -3673,98 +3673,98 @@
         <v>124</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.07408348150030264</v>
+        <v>-0.0615611918246799</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.07275386865810418</v>
+        <v>-0.05984405908205304</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.4676225752546941</v>
+        <v>-0.454615443837092</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.275533783159254</v>
+        <v>1.288512925557718</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-5.417058397423055</v>
+        <v>-5.40401550112869</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-2.275985663082437</v>
+        <v>-2.262919408781961</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-3.549620674767162</v>
+        <v>-3.536439665471924</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3848141093365598</v>
+        <v>-0.3716153703817966</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.234939294364487</v>
+        <v>-1.221534166711656</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1732106071243962</v>
+        <v>0.1866679008346139</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-5.437567525852764</v>
+        <v>-5.424115237132654</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-5.051370523894441</v>
+        <v>-5.037814477542838</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-5.608100804521378</v>
+        <v>-5.61853044021953</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.08562</t>
+          <t>X &gt; 0.08561</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-1.302962129733785</v>
+        <v>-1.290439840058163</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-8.866916695078991</v>
+        <v>-8.85400688550294</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-8.071309211199392</v>
+        <v>-8.058302079781789</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-6.750579888115709</v>
+        <v>-6.737600745717245</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-13.24138205556882</v>
+        <v>-13.22827125119388</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-10.56298773690079</v>
+        <v>-10.54994484060642</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-9.457245263696869</v>
+        <v>-9.444179009396393</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-11.11490485295457</v>
+        <v>-11.10172384365933</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-6.413999977232102</v>
+        <v>-6.400801238277339</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-4.88317278130765</v>
+        <v>-4.869767653654819</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-3.897449915149032</v>
+        <v>-3.883992621438814</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-9.815447710184557</v>
+        <v>-9.801995421464447</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-11.42617851160565</v>
+        <v>-11.41262246525405</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-12.36693336980556</v>
+        <v>-12.37736300550371</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MACD-12-26 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MACD-12-26 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.0999636495819658</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.656892828730534</v>
+        <v>0.6698026383065852</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.452500312610134</v>
+        <v>1.465507444027736</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.344658207122386</v>
+        <v>6.35763734952085</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5.806236992050216</v>
+        <v>5.819347796425156</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>7.209421402969795</v>
+        <v>7.222487657270271</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.7898570518073456</v>
+        <v>0.8030380611025834</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.919333356101227</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.640636742501869</v>
+        <v>4.6540418701547</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>6.816835799136676</v>
+        <v>6.830293092846894</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>11.61312371838687</v>
+        <v>11.62657600710698</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.19286910744197</v>
+        <v>11.20642515379357</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>9.06163805876588</v>
+        <v>9.051208423067727</v>
       </c>
     </row>
     <row r="7">
@@ -3963,150 +3963,150 @@
         <v>90</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2712160979877467</v>
+        <v>-0.258693808312124</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.3394325112702106</v>
+        <v>0.3523423208462617</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.055674915784735</v>
+        <v>1.068682047202337</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.741483603947792</v>
+        <v>6.754462746346256</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.31417349998673</v>
+        <v>7.327284304361669</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.389393215480169</v>
+        <v>5.402436111774534</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.637992831541219</v>
+        <v>8.651059085841695</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.615253877204161</v>
+        <v>2.628434886499399</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.665365102132981</v>
+        <v>3.678563841087744</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.148573250438382</v>
+        <v>6.161978378091213</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.277153259454138</v>
+        <v>9.290610553164356</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.5337586390218</v>
+        <v>11.54721092774191</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>12.224615139188</v>
+        <v>12.2381711855396</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.36322536035318</v>
+        <v>11.35279572465503</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.09482</t>
+          <t>X &lt; -0.09481</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>107</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.712169156425531</v>
+        <v>1.724691446101154</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.904333861218284</v>
+        <v>2.917243670794335</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.313203472378703</v>
+        <v>5.326210603796305</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.378036044238542</v>
+        <v>6.391015186637006</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.708773707671043</v>
+        <v>7.721884512045982</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.137056766882033</v>
+        <v>6.150099663176398</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9.790640806619102</v>
+        <v>9.803707060919578</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.650560211575915</v>
+        <v>4.663741220871152</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.720401446888943</v>
+        <v>2.733600185843706</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.543173458122695</v>
+        <v>6.556578585775526</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>11.94589676931913</v>
+        <v>11.95935406302935</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>13.84943880516924</v>
+        <v>13.86289109388935</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>11.56002531571966</v>
+        <v>11.57358136207127</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>10.87516720874362</v>
+        <v>10.86473757304547</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.08814</t>
+          <t>X &lt; -0.08813</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>126</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.6811648543932023</v>
+        <v>0.693687144068825</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1367579649202639</v>
+        <v>-0.1238481553442128</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.360531222995412</v>
+        <v>4.373510365393876</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.203062388875622</v>
+        <v>6.216173193250562</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.119551945638904</v>
+        <v>4.132594841933269</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.828469022017416</v>
+        <v>4.841535276317892</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.186682448632737</v>
+        <v>1.199863457927975</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.332031768799645</v>
+        <v>0.3452305077544082</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.243811345676477</v>
+        <v>4.257216473329308</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.800962783263657</v>
+        <v>8.814420076973875</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>9.208742123314984</v>
+        <v>9.222298169666587</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>8.664812661940474</v>
+        <v>8.654383026242321</v>
       </c>
     </row>
     <row r="10">
@@ -4119,202 +4119,202 @@
         <v>147</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.928330387273022</v>
+        <v>1.940852676948644</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.043787443378314</v>
+        <v>-1.030877633802262</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.003520720773395</v>
+        <v>4.016527852190997</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.814045962224434</v>
+        <v>4.827025104622898</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.915080529465186</v>
+        <v>2.928191333840125</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.17170614065023</v>
+        <v>1.184749036944595</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4067003145344117</v>
+        <v>0.4197665688348877</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.101299410777692</v>
+        <v>-2.088118401482454</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.8017550792729153</v>
+        <v>-0.7885563403181521</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.429752388760377</v>
+        <v>2.443157516413208</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.306631717504025</v>
+        <v>6.320089011214243</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>7.021286983692995</v>
+        <v>7.034739272413105</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.920760263904555</v>
+        <v>5.934316310256158</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.850753705024381</v>
+        <v>6.840324069326229</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.07477</t>
+          <t>X &lt; -0.07476</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>159</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.9656811766453686</v>
+        <v>0.9782034663209913</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.532684889149074</v>
+        <v>-2.519775079573023</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.103892945134838</v>
+        <v>2.11690007655244</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.8630768953524</v>
+        <v>2.876056037750864</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.4378632274500447</v>
+        <v>0.450974031824984</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.5225564700544254</v>
+        <v>-0.50951357376006</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.6072901873267043</v>
+        <v>-0.5942239330262282</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.703404403718267</v>
+        <v>-1.690223394423029</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.135473472290506</v>
+        <v>-1.122274733335743</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.159055430731883</v>
+        <v>1.172460558384714</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.356817829684744</v>
+        <v>5.370275123394961</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.391200987030174</v>
+        <v>5.404653275750285</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.342015558475211</v>
+        <v>4.355571604826814</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.22066770836156</v>
+        <v>5.210238072663408</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.06809</t>
+          <t>X &lt; -0.06808</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>190</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.717087995579497</v>
+        <v>1.72961028525512</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.9997487752795</v>
+        <v>-1.986838965703448</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.342224623387068</v>
+        <v>2.35523175480467</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.472477755994568</v>
+        <v>2.485456898393032</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.934056540922398</v>
+        <v>1.947167345297338</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4000804687303585</v>
+        <v>-0.3870375724359931</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.04150160347105469</v>
+        <v>0.05456785777153073</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.004629163731508</v>
+        <v>-1.99144815443627</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.01299747096644</v>
+        <v>-0.9997987320116763</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2421405019003657</v>
+        <v>0.2555456295531968</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.247913493372266</v>
+        <v>4.261370787082484</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.282296650717697</v>
+        <v>4.295748939437807</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.862042039772795</v>
+        <v>3.875598086124398</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>5.164394950996453</v>
+        <v>5.153965315298301</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.06141</t>
+          <t>X &lt; -0.0614</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.816906507376231</v>
+        <v>1.829428797051854</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.498436342687832</v>
+        <v>1.511346152263883</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.844946946436075</v>
+        <v>5.857954077853677</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.544165596284955</v>
+        <v>5.557144738683419</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.005744381212786</v>
+        <v>5.018855185587725</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.285944939618105</v>
+        <v>2.29898783591247</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.770176739587207</v>
+        <v>1.783242993887683</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.8719588580470727</v>
+        <v>0.8851398673423105</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.241993454623405</v>
+        <v>1.255192193578168</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.684971717871335</v>
+        <v>1.698376845524166</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.359528738381343</v>
+        <v>5.372986032091561</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.531842930209528</v>
+        <v>4.545295218929638</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.673388587961448</v>
+        <v>5.418247813892094</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.889795408662359</v>
+        <v>5.046879418738712</v>
       </c>
     </row>
     <row r="14">
@@ -4324,153 +4324,153 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.114070212213235</v>
+        <v>2.126592501888858</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.891575097542493</v>
+        <v>2.904484907118544</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.25097260255</v>
+        <v>6.263979733967602</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.333444165191622</v>
+        <v>4.346423307590086</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5.160210663430043</v>
+        <v>5.173321467804982</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.751167959507477</v>
+        <v>3.764210855801842</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.98384038557991</v>
+        <v>2.996906639880386</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.857953915126046</v>
+        <v>2.871134924421284</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.114360172288457</v>
+        <v>2.12755891124322</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.312016557226393</v>
+        <v>3.325421684879224</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.022967566912278</v>
+        <v>4.827205168257265</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.955293576020644</v>
+        <v>5.755734519827136</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.749519353747388</v>
+        <v>5.548595011427345</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.485101561814155</v>
+        <v>4.609500705497936</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.04804</t>
+          <t>X &lt; -0.04803</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.6857524312351089</v>
+        <v>0.6982747209107316</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.8082828645136289</v>
+        <v>0.82119267408968</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.436535545200272</v>
+        <v>2.449542676617874</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.121701972605457</v>
+        <v>1.134681115003922</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.473454167937916</v>
+        <v>3.486564972312856</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.192861423572658</v>
+        <v>3.205904319867024</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.952058342138528</v>
+        <v>1.965124596439004</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.617822920235632</v>
+        <v>0.6310039295308698</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.02121164802758813</v>
+        <v>-0.008012909072824925</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.4214750587403628</v>
+        <v>-0.5689143643622288</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.279737238782303</v>
+        <v>1.126359345434885</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.648109141127392</v>
+        <v>2.490363382522268</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.400053735679229</v>
+        <v>2.241410576534093</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.649963711607661</v>
+        <v>1.762152449801221</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.04136</t>
+          <t>X &lt; -0.04135</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.11961529284364</v>
+        <v>1.132137582519263</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.372843544681245</v>
+        <v>1.385753354257297</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.609676469786287</v>
+        <v>2.622683601203889</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.807528669992848</v>
+        <v>1.820507812391313</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.60010978592301</v>
+        <v>3.613220590297949</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.431351257438209</v>
+        <v>3.444394153732574</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.481815675364061</v>
+        <v>1.494881929664537</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.3839691220188328</v>
+        <v>-0.370788112723595</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1503079889450234</v>
+        <v>0.03443019695409077</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1324400211903978</v>
+        <v>0.01452251100917579</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.233334793100454</v>
+        <v>1.112104177936665</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.108922037714599</v>
+        <v>1.985395591278674</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.354594174827419</v>
+        <v>1.231635237827184</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.032256093213704</v>
+        <v>1.122187758198002</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.335164938915014</v>
+        <v>-0.3226426492393912</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.946738551879271</v>
+        <v>-1.93382874230322</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3562344681428513</v>
+        <v>0.3692415995604534</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3066314856424341</v>
+        <v>0.3196106280408983</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.668527854341086</v>
+        <v>1.579882226024345</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.346071915841179</v>
+        <v>1.258291967630385</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4583665506491172</v>
+        <v>0.3718773770571104</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.8146978136170944</v>
+        <v>-0.8997949708443755</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5955746034528318</v>
+        <v>-0.6813395405547737</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.4372853354201993</v>
+        <v>-0.5248536444939873</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3700494343175293</v>
+        <v>0.2805095430633457</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.602696189711168</v>
+        <v>1.510781055246461</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.3741174751619951</v>
+        <v>0.283588865993778</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.277755274883084</v>
+        <v>1.34467059769991</v>
       </c>
     </row>
     <row r="18">
@@ -4532,309 +4532,309 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.01013821770132495</v>
+        <v>-0.052344601962929</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.239682420280246</v>
+        <v>-1.302402552782731</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1629601062836983</v>
+        <v>0.09765371227715747</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2280736422619682</v>
+        <v>0.1627203583341341</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.07036854395156</v>
+        <v>2.001613806277383</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.864897538246737</v>
+        <v>0.7981195650119446</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1387143322627225</v>
+        <v>0.07276898017406808</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.260789796527369</v>
+        <v>-1.325389067324558</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.664913077638694</v>
+        <v>-0.730556261673982</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.435967812363543</v>
+        <v>-1.50163313501379</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.835731759091253</v>
+        <v>-0.9026261618114972</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.005980861244012203</v>
+        <v>-0.06220690809103502</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.205758465858096</v>
+        <v>-1.272810726605101</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.1463308430805768</v>
+        <v>-0.0931043238651128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.02131</t>
+          <t>X &lt; -0.0213</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.115268529691782</v>
+        <v>-1.159330127450652</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.897506414410437</v>
+        <v>-1.942157250389805</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6877259436382275</v>
+        <v>-0.7341141264547701</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.8298044983137558</v>
+        <v>-0.87598538133944</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.6844208237224336</v>
+        <v>0.636035533466881</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9520701991539724</v>
+        <v>-0.9984498239951165</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.754164031203871</v>
+        <v>-1.799790877203385</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.940301678351382</v>
+        <v>-2.985080960090798</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.943212329581279</v>
+        <v>-2.98810282557892</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.289684606527722</v>
+        <v>-3.33499356604424</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.651869408698964</v>
+        <v>-1.699243443371159</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.333304853041696</v>
+        <v>-1.381068522276685</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.915670397745586</v>
+        <v>-1.963217703349287</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.380995370444737</v>
+        <v>-1.341183170441184</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.01463</t>
+          <t>X &lt; -0.01462</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.58277049713972</v>
+        <v>-1.614364904017883</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.195289710952011</v>
+        <v>-2.227401343025768</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.67624901509663</v>
+        <v>-1.709095730575442</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.152236202815494</v>
+        <v>-1.185492847823063</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2518259197985842</v>
+        <v>-0.2862422656866386</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.300502254903108</v>
+        <v>-1.333856316423898</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.21059769446866</v>
+        <v>-2.243249857247733</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.370202783645169</v>
+        <v>-2.403048209499822</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.559768328240629</v>
+        <v>-2.592524000680733</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.664558062692933</v>
+        <v>-2.69779842928385</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.597737379216028</v>
+        <v>-1.632077869524068</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.953301100227094</v>
+        <v>-1.98734725248557</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.676543688351195</v>
+        <v>-2.710262361843156</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.204026101635129</v>
+        <v>-2.174324734980772</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.007942</t>
+          <t>X &lt; -0.00794</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.760709778688685</v>
+        <v>-1.783565960799351</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.638531486246855</v>
+        <v>-2.661536875866155</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.368503980092278</v>
+        <v>-2.391901441314118</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.712284849820669</v>
+        <v>-1.736103291389604</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6743188411998062</v>
+        <v>-0.6991337220563523</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.039178213091262</v>
+        <v>-1.063624070170874</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.927295652457836</v>
+        <v>-1.951181810516843</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.497727266632516</v>
+        <v>-2.521452211530651</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.311243085001522</v>
+        <v>-2.335149732233127</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.211289421222041</v>
+        <v>-2.235682440622234</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.39435450973459</v>
+        <v>-1.419439384413671</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.532345439740517</v>
+        <v>-1.557341270274812</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.7029788869282</v>
+        <v>-1.728073540198793</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.555397487847131</v>
+        <v>-1.534060167126974</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; -0.00126</t>
+          <t>X &lt; -0.001257</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-3.025651205364035</v>
+        <v>-3.04082644486806</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.871828076671996</v>
+        <v>-2.887620330881099</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.340598530965437</v>
+        <v>-2.356828665303894</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.181075318611136</v>
+        <v>-2.197366255959473</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.679525420719486</v>
+        <v>-1.696284719207348</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.857797795755786</v>
+        <v>-1.874374668685888</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.98089418363584</v>
+        <v>-2.996880989064664</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.519104328020184</v>
+        <v>-2.535514898023735</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.719303190244936</v>
+        <v>-2.735634384134102</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.976802124936995</v>
+        <v>-2.993277046156898</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.362909338354939</v>
+        <v>-2.379809867256071</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.129024775734571</v>
+        <v>-2.146059807782365</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.011143462052836</v>
+        <v>-2.028395268174542</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.843446322616472</v>
+        <v>-1.828253344718924</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.005423</t>
+          <t>X &lt; 0.005425</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.882536064570871</v>
+        <v>-1.89378592250241</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.341965388745464</v>
+        <v>-2.353380319086902</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.195082897531869</v>
+        <v>-2.206666644225344</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.228451036575088</v>
+        <v>-2.239997376994395</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.424056255192177</v>
+        <v>-1.436114388448786</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.666659540054447</v>
+        <v>-1.678543172594587</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.480448890105023</v>
+        <v>-2.491977497609398</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.168653084920614</v>
+        <v>-2.180445624548874</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.968806805623835</v>
+        <v>-1.980716372647919</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.321879269093898</v>
+        <v>-2.333828749791387</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.793038745582059</v>
+        <v>-1.805294223722015</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.780155180324243</v>
+        <v>-1.79241765267988</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.032893787508073</v>
+        <v>-2.045143777983206</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.710060691656281</v>
+        <v>-1.699084132517839</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.786871404166746</v>
+        <v>-1.79541540735196</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.337860166022466</v>
+        <v>-2.346466213373738</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.087235049088626</v>
+        <v>-2.096021117500825</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.268087765174144</v>
+        <v>-2.276781476245723</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.827282693925746</v>
+        <v>-1.836261263678281</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.090823360946324</v>
+        <v>-2.099645486893245</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.653673835125446</v>
+        <v>-2.66228257735419</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.557271712161779</v>
+        <v>-2.566009557945037</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.512931626622475</v>
+        <v>-2.521704789360129</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.631846718967822</v>
+        <v>-2.640727580578051</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.271724499774209</v>
+        <v>-2.280798152161751</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.17303792790004</v>
+        <v>-2.182152826663597</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.278308837420184</v>
+        <v>-2.287460918380603</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.922283299163006</v>
+        <v>-1.913703857634033</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2705</v>
+        <v>2706</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.831186664580834</v>
+        <v>-1.83729705296907</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.804680685474558</v>
+        <v>-1.81101308754225</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.664829093379069</v>
+        <v>-1.671268061168824</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.030769311951531</v>
+        <v>-2.037060735898876</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.70244813269975</v>
+        <v>-1.708934234619299</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.827709622706337</v>
+        <v>-1.834115104142931</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.298585339550215</v>
+        <v>-2.304832301306604</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.377573697696441</v>
+        <v>-2.38385616561466</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.566697218490233</v>
+        <v>-2.572921875539997</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.806760821174755</v>
+        <v>-2.813011371806283</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.437929622541596</v>
+        <v>-2.444346995746685</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.346715850983543</v>
+        <v>-2.353166554614901</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.599233099294388</v>
+        <v>-2.605649362012009</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.514367574541055</v>
+        <v>-2.507761062731028</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.259479781216889</v>
+        <v>-1.263810767376462</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.405867759375681</v>
+        <v>-1.410298898853199</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.487039019751066</v>
+        <v>-1.491481803284096</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.833395623105353</v>
+        <v>-1.837715207043424</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.629630270835158</v>
+        <v>-1.634068352643155</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.710145347473031</v>
+        <v>-1.71453258674277</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.074173340565601</v>
+        <v>-2.078450911960978</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.260149230388919</v>
+        <v>-2.264410481123413</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.435664994278184</v>
+        <v>-2.439876498988482</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.575299136800346</v>
+        <v>-2.579544405002011</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.432248449947572</v>
+        <v>-2.436562164107372</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.413107646021508</v>
+        <v>-2.417427199986356</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.650398625815853</v>
+        <v>-2.654680715238321</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.448921221125858</v>
+        <v>-2.444142938487808</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3255</v>
+        <v>3256</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.963450560112058</v>
+        <v>-0.9666914970378784</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.9675769775574636</v>
+        <v>-0.9709270929984299</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.039990866347672</v>
+        <v>-1.043347337554323</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.567177277454292</v>
+        <v>-1.570365449884271</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.231578134000202</v>
+        <v>-1.234907289989195</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.254799245445355</v>
+        <v>-1.258103103911736</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.445800342380707</v>
+        <v>-1.449053285187006</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.528669254759436</v>
+        <v>-1.531930260990208</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.542542191663884</v>
+        <v>-1.545804961937918</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.762510585775864</v>
+        <v>-1.765765316523648</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.705044407826399</v>
+        <v>-1.708332544582063</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.653905537282242</v>
+        <v>-1.657208961760858</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.934544019971163</v>
+        <v>-1.937791697822725</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.760174537240268</v>
+        <v>-1.756677384818083</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3436</v>
+        <v>3437</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.826288421688659</v>
+        <v>-0.8287421174908758</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.7407427916429157</v>
+        <v>-0.7433053709162465</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.8590335263388553</v>
+        <v>-0.861583485151364</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.322616479885319</v>
+        <v>-1.325026664735852</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.9167569950947012</v>
+        <v>-0.9193140060787712</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.9520701991539724</v>
+        <v>-0.9546030754533348</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.166441285991937</v>
+        <v>-1.168917685354586</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.298491361352227</v>
+        <v>-1.300954857586824</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.285715010237453</v>
+        <v>-1.288186756110271</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.480625715969886</v>
+        <v>-1.48308604116675</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.495035038177612</v>
+        <v>-1.497503141926089</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.473803897336559</v>
+        <v>-1.47627781252497</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.87812303686993</v>
+        <v>-1.880502461929858</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.699767784130067</v>
+        <v>-1.697021622514661</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3590</v>
+        <v>3591</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5089809235960416</v>
+        <v>-0.5108827341969473</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.6069552979715738</v>
+        <v>-0.6088936861849135</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7092669213592728</v>
+        <v>-0.7111933306741562</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.064071951607772</v>
+        <v>-1.065895796033956</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.6151895947000625</v>
+        <v>-0.617160140082774</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.4972104532246675</v>
+        <v>-0.4992032324877584</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5947010800517702</v>
+        <v>-0.5966711346511673</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.7965617203733899</v>
+        <v>-0.7984949624487925</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.7589897116516013</v>
+        <v>-0.7609368386799105</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.09312587773821</v>
+        <v>-1.095014358734623</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.171249498995934</v>
+        <v>-1.173125302892032</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.23288328129496</v>
+        <v>-1.234741634338683</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.52642913817207</v>
+        <v>-1.528223271278023</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.456335147229616</v>
+        <v>-1.454221819204626</v>
       </c>
     </row>
     <row r="30">
@@ -5156,101 +5156,101 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3731</v>
+        <v>3732</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5970707988424522</v>
+        <v>-0.5984060171832155</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.5917872470935492</v>
+        <v>-0.5931704996665559</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7852895120316461</v>
+        <v>-0.7866330595153883</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.068371158593422</v>
+        <v>-1.069636071873354</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7101877596686421</v>
+        <v>-0.7115644882962684</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.5587212536292228</v>
+        <v>-0.5601307331452503</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.575490314526192</v>
+        <v>-0.5768984785694613</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.6803189233191347</v>
+        <v>-0.68171314274975</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.5126030158779642</v>
+        <v>-0.5140446089464561</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.6251884630823668</v>
+        <v>-0.6266250004479232</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.6811875130269627</v>
+        <v>-0.6826156851221299</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.6854871269692211</v>
+        <v>-0.6869139309142867</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.9300829672786008</v>
+        <v>-0.9314570550771251</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.8798432241788205</v>
+        <v>-0.8783582589105379</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.05889</t>
+          <t>X &lt; 0.05888</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3835</v>
+        <v>3836</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3364736632453216</v>
+        <v>-0.337502156800916</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3228440101173078</v>
+        <v>-0.3239108554069148</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4697194333225667</v>
+        <v>-0.4707570539731805</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.7415390806353699</v>
+        <v>-0.7425037989822272</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.3815138627141579</v>
+        <v>-0.3825842117487142</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.1739687413244155</v>
+        <v>-0.1750873013368093</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3226179614485361</v>
+        <v>-0.323700216786456</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.489261729264058</v>
+        <v>-0.4903111369837347</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4318571200892407</v>
+        <v>-0.4329233294986281</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4602079715233529</v>
+        <v>-0.4612855107976728</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5201948964140897</v>
+        <v>-0.5212617515446283</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.3670319091495173</v>
+        <v>-0.3681385019379064</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4077565442785698</v>
+        <v>-0.4088620869823316</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.3258953118183499</v>
+        <v>-0.3248777778360008</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3932</v>
+        <v>3933</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1740466852289799</v>
+        <v>-0.1747832378328908</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.07357177090242573</v>
+        <v>-0.07435814387701356</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.09967774857123146</v>
+        <v>-0.100463772044904</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2854062996544471</v>
+        <v>-0.2861436729058724</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.02350165296373063</v>
+        <v>-0.02431386915431233</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2117282408608787</v>
+        <v>0.2108603695771265</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.09013804606266973</v>
+        <v>0.08929935656928478</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.03301653642937197</v>
+        <v>-0.03383134012325684</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.1054135505354381</v>
+        <v>-0.1062112844695093</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1285270205643272</v>
+        <v>-0.1293319823072778</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1665852694178085</v>
+        <v>-0.1673840267814413</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.009158288798666092</v>
+        <v>0.008314979697289004</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.06625696861775054</v>
+        <v>-0.06708781011085563</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.01983211970662779</v>
+        <v>0.02047942666366254</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3989</v>
+        <v>3990</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1446127330035836</v>
+        <v>-0.1451678416759989</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1185085590177763</v>
+        <v>-0.1190886303448053</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.07488063977081794</v>
+        <v>-0.07547635764089478</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.231092873504906</v>
+        <v>-0.2316483647648582</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.01941500963044263</v>
+        <v>0.01879051424747047</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1554677713970989</v>
+        <v>0.1548122998685741</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.05941425296264669</v>
+        <v>0.05878154435225014</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.05649987915104049</v>
+        <v>0.05586231392683771</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1158622945175551</v>
+        <v>-0.1164577136334373</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1006963046162994</v>
+        <v>-0.1013054365195956</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1411277470032246</v>
+        <v>-0.1417293750433473</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.08271601534072914</v>
+        <v>0.08205840046512236</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1026435435321957</v>
+        <v>0.101975857161861</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1660442233374937</v>
+        <v>0.1664966436191051</v>
       </c>
     </row>
     <row r="34">
@@ -5364,101 +5364,101 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4054</v>
+        <v>4055</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.002258753800354896</v>
+        <v>0.001876496505957448</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.00221876038208535</v>
+        <v>0.001824603719249751</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.01426450168060001</v>
+        <v>0.01386431751986805</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.03891884574599658</v>
+        <v>-0.03930519133312771</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.149790312960171</v>
+        <v>0.1493534207221217</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1653656428558463</v>
+        <v>0.1649268821412591</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.06949574543763504</v>
+        <v>0.06907976530994375</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.108412060017514</v>
+        <v>0.1079828905487616</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.01175583876761266</v>
+        <v>0.01134982904614645</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.03773594689531024</v>
+        <v>0.03731713147875126</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.005294088065923575</v>
+        <v>-0.005703996969813829</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.166237271500421</v>
+        <v>0.1657851341889227</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1544685437639757</v>
+        <v>0.1540160244613631</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1715353970795945</v>
+        <v>0.1718120282582518</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.08562</t>
+          <t>X &lt; 0.08561</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.02664933501281297</v>
+        <v>0.02638679322416237</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1813981983406308</v>
+        <v>0.1810899874317613</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1651619911670537</v>
+        <v>0.1648556684612004</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1381697637918364</v>
+        <v>0.1378705146504871</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.271088494435233</v>
+        <v>0.2707540899367231</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2163069161140072</v>
+        <v>0.2159871719743833</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1937109490735338</v>
+        <v>0.1933961571890066</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2277200018654213</v>
+        <v>0.2273944898481801</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1314408387625079</v>
+        <v>0.1311383668329995</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1000943176256328</v>
+        <v>0.09979518977970514</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.07990866313704714</v>
+        <v>0.07961331874105326</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2012933612440122</v>
+        <v>0.2009684196736643</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.234383148956006</v>
+        <v>0.2340479216507134</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.2537426485255665</v>
+        <v>0.2538946257539223</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/macd/macd_12_26.xlsx
+++ b/workspaces/btc_daily_14days/macd/macd_12_26.xlsx
@@ -568,1197 +568,1197 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.1048</t>
+          <t>X ≈ -0.1047</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.473047068800405</v>
+        <v>7.466263441727939</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.080168245833555</v>
+        <v>-14.05223298647675</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.474915992290754</v>
+        <v>-14.44837287122736</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.27966915898204</v>
+        <v>5.628784836017331</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>28.37567761561089</v>
+        <v>25.09822723949058</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>28.67950925238171</v>
+        <v>25.3767066206406</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>28.60184211343055</v>
+        <v>25.32223194261472</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>28.14267111764402</v>
+        <v>24.86347762586343</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>28.08861331529906</v>
+        <v>24.83258511696489</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>27.24634288392284</v>
+        <v>24.0155683988995</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>43.702888530593</v>
+        <v>43.80280070720303</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.43088129927875</v>
+        <v>3.891109222901854</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>26.67603557254408</v>
+        <v>23.49218280102126</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>43.57501794687725</v>
+        <v>43.74701670643481</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.09816</t>
+          <t>X ≈ -0.09804</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>17</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>12.18607996358072</v>
+        <v>12.15708324224517</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>16.44763993165233</v>
+        <v>16.44658702237034</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>27.79093056501788</v>
+        <v>27.79097964761483</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.455574859070524</v>
+        <v>4.45511295660279</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9.788953062418337</v>
+        <v>9.837449935068854</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.08826553263467</v>
+        <v>10.11222960652195</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>15.87833850811961</v>
+        <v>15.92634137664484</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>15.41609201999957</v>
+        <v>15.46532729836462</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.266464886668601</v>
+        <v>-2.193306297747327</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.63702110667127</v>
+        <v>8.736292615992639</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>26.06863985374963</v>
+        <v>26.16852543856524</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>26.10942567286163</v>
+        <v>26.23309560513967</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.053120833178312</v>
+        <v>8.201778855892961</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.280900299821106</v>
+        <v>8.452899059385082</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.09147</t>
+          <t>X ≈ -0.09135</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>19</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.096293513813968</v>
+        <v>-5.125437107703831</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-17.19929998767974</v>
+        <v>-17.20061940128741</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-12.34847493326325</v>
+        <v>-12.34871633133136</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.971439958141858</v>
+        <v>-6.971977426571435</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.258792725914937</v>
+        <v>-2.210368011250644</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-7.215219460153371</v>
+        <v>-7.191347110096942</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-23.06393695351243</v>
+        <v>-23.01611523318432</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-18.2803568169679</v>
+        <v>-18.23125592075246</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-13.08900309353646</v>
+        <v>-13.0158815340908</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-8.683422787001881</v>
+        <v>-8.584197964224522</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-8.89017594739969</v>
+        <v>-8.790360083700328</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.857954404433571</v>
+        <v>-8.734331078479983</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.018222353841551</v>
+        <v>-3.869572620750006</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.793403105756724</v>
+        <v>-3.621404346185273</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.08479</t>
+          <t>X ≈ -0.08467</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>21</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.393490015079188</v>
+        <v>9.36447320091218</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-6.453835236479549</v>
+        <v>-6.455070569059707</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.14643091983282</v>
+        <v>12.14636908611787</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.529103785039794</v>
+        <v>7.528663047220107</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-16.76271345494248</v>
+        <v>-16.71437794797347</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-16.46990182381921</v>
+        <v>-16.44608054976027</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-26.06585331707878</v>
+        <v>-26.01804868936899</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-21.78364883990423</v>
+        <v>-21.73456427997689</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.581888578001049</v>
+        <v>-7.508750233127458</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-8.432961360844935</v>
+        <v>-8.333737300001779</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.639672791043679</v>
+        <v>-8.539857503070763</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-13.36695441149731</v>
+        <v>-13.2433380056605</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-13.79022574082717</v>
+        <v>-13.64158301869156</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.044029672168207</v>
+        <v>-3.872030912603705</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.0781</t>
+          <t>X ≈ -0.07799</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>12</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-10.77961799397074</v>
+        <v>-10.80881011802339</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-20.69687521483023</v>
+        <v>-20.69822704986668</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-21.0962138218886</v>
+        <v>-21.09652171031209</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-20.97158360430233</v>
+        <v>-20.97221646760974</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-29.82839640175915</v>
+        <v>-29.78014308544359</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-21.22208334116168</v>
+        <v>-21.19828966011524</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-12.9930095398995</v>
+        <v>-12.94514559945971</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.179358587742243</v>
+        <v>3.228542612423027</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.20381692495743</v>
+        <v>-5.130671699817597</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-14.37935790111621</v>
+        <v>-14.28015116276899</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.260444855928441</v>
+        <v>-6.160625624420057</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-14.55678553768406</v>
+        <v>-14.43317154762217</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-14.98037838077522</v>
+        <v>-14.83173692458748</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-14.75831538645988</v>
+        <v>-14.58631662688564</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.07142</t>
+          <t>X ≈ -0.07131</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>31</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.565337192007171</v>
+        <v>5.53629009533384</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.7446663148603889</v>
+        <v>0.7434877315401138</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.567574479419022</v>
+        <v>3.567449761274773</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4805721066048463</v>
+        <v>0.4800837512799916</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>9.599492541431523</v>
+        <v>9.647984834804937</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.2407033905718592</v>
+        <v>0.2646122027199098</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.376358133057067</v>
+        <v>3.424298676171603</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.531028112800001</v>
+        <v>-3.48187234812697</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3710946534209469</v>
+        <v>-0.2979341847322132</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.442931889775657</v>
+        <v>-4.343699709171332</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.425323009856584</v>
+        <v>-1.325494873136698</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.391266745489112</v>
+        <v>-1.267635710627872</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.413400924884478</v>
+        <v>1.562053054350102</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.865340527522406</v>
+        <v>5.037339287086141</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.06474</t>
+          <t>X ≈ -0.06464</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.331289839922746</v>
+        <v>3.292759410057322</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>17.70793343913337</v>
+        <v>17.94559803263727</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>22.17922571643252</v>
+        <v>22.19514909160152</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>19.88461716066301</v>
+        <v>20.01059412788726</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>19.33879970608753</v>
+        <v>19.5275830096026</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>14.7758810454639</v>
+        <v>15.1632141988499</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9.822801352553441</v>
+        <v>10.46349779197861</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>14.21706299913713</v>
+        <v>14.64527956689054</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>11.72277555105907</v>
+        <v>12.28931948728567</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>8.419980848208624</v>
+        <v>9.146120018110892</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>10.65486869106597</v>
+        <v>11.26812362829708</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.81605309651011</v>
+        <v>6.680344926493063</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>12.70376606705129</v>
+        <v>13.26201387680045</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.550627702974808</v>
+        <v>1.886551590164842</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.05806</t>
+          <t>X ≈ -0.05796</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.361901448774063</v>
+        <v>2.481220224304913</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>8.464256081918734</v>
+        <v>7.54982221576379</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>8.067231731928679</v>
+        <v>7.158434644549168</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2561240266370604</v>
+        <v>-1.022050278355792</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.956414733546822</v>
+        <v>5.141024080044239</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9.645363410710488</v>
+        <v>8.741479266195306</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7.866217470798667</v>
+        <v>7.019582074266573</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>10.77120993889552</v>
+        <v>9.88458424852093</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.629567708105697</v>
+        <v>4.856586541191945</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>9.836844624727064</v>
+        <v>9.029715615196466</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.855415435282559</v>
+        <v>2.166373290037448</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>10.61750882670625</v>
+        <v>8.888421988133693</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.061146703430374</v>
+        <v>3.496987937209937</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.897051845183107</v>
+        <v>0.413683373112093</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.05138</t>
+          <t>X ≈ -0.05128</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-7.316458516096795</v>
+        <v>-7.032303297868154</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-10.87514806867864</v>
+        <v>-12.23756431124086</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-18.95346106887791</v>
+        <v>-19.88598153996428</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-16.90821541874258</v>
+        <v>-17.94764047678546</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.935897969865557</v>
+        <v>-7.556880092688807</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1267331567167176</v>
+        <v>-1.843087830191671</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.803644319390983</v>
+        <v>-5.533687642232664</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-11.96885529328789</v>
+        <v>-13.26154550801321</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-12.03511704553989</v>
+        <v>-13.30179016518646</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-22.51812401023906</v>
+        <v>-23.20972738698745</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-19.72648346392967</v>
+        <v>-21.60300290160691</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-15.84595146542049</v>
+        <v>-17.91594740325166</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-16.2661023187339</v>
+        <v>-18.31554594121415</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-14.11728974543132</v>
+        <v>-16.25298329355692</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.04469</t>
+          <t>X ≈ -0.04461</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>82</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.970936468615918</v>
+        <v>2.359575723195555</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.778542993900416</v>
+        <v>4.42901593801426</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.382170052039591</v>
+        <v>4.037186804260102</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4.731372961658977</v>
+        <v>5.384438501009122</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.190739685746784</v>
+        <v>4.897291246787567</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.492411685469229</v>
+        <v>5.170931826393208</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.4687677624422903</v>
+        <v>0.2430496692245612</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.600480094999014</v>
+        <v>-3.874452402951746</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2139304714602943</v>
+        <v>0.9592477571819842</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.476341521723199</v>
+        <v>2.573027482430788</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.052128168341056</v>
+        <v>1.151064976464504</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.133005874426118</v>
+        <v>-0.009397631619499691</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.992181117983428</v>
+        <v>-2.842772697450577</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.546933272634391</v>
+        <v>-1.374934513068837</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.03801</t>
+          <t>X ≈ -0.03793</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.397125488615018</v>
+        <v>-4.183927744988267</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-13.55856437518877</v>
+        <v>-12.0431898583613</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-7.464642099443836</v>
+        <v>-5.484568283899605</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-4.896786138720103</v>
+        <v>-3.03038894282507</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5.447216784623755</v>
+        <v>-3.887426410780094</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-6.32612561237422</v>
+        <v>-5.507091871815156</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.536121050532593</v>
+        <v>-3.607324019454161</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.752527389576777</v>
+        <v>-3.666435039234749</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.177804722597891</v>
+        <v>-4.825163711655129</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.401707258765342</v>
+        <v>-4.453154403406579</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.606408417025719</v>
+        <v>-4.223639455727024</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.133005874426118</v>
+        <v>-2.617155264561212</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.992181117983066</v>
+        <v>-5.337789667729986</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.111603312730537</v>
+        <v>-0.4390298051836439</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.03133</t>
+          <t>X ≈ -0.03126</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>140</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.018219597314094</v>
+        <v>0.6131754343212705</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.171014402241944</v>
+        <v>0.3933919008952671</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.9787360761650348</v>
+        <v>-2.469538197237313</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.4588464694402106</v>
+        <v>-1.948541552008734</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.676490653568344</v>
+        <v>1.127151519477273</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.026135316796577</v>
+        <v>-2.167363850138528</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.110845676062894</v>
+        <v>-2.232737291356948</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.006485748421561</v>
+        <v>-2.713311776718449</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.9246107620870205</v>
+        <v>-1.322302626283097</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-5.34595812984513</v>
+        <v>-5.73524984850058</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-5.550659288105493</v>
+        <v>-5.941159303034347</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.192788989575426</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-7.365003417635329</v>
+        <v>-7.620656223538887</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-5.710696338837046</v>
+        <v>-5.538697579270533</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.02465</t>
+          <t>X ≈ -0.02458</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>208</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.884762184380612</v>
+        <v>-4.685688968247483</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-3.612519679273497</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.52533504681476</v>
+        <v>-3.525488436819082</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.356648364764972</v>
+        <v>-4.357142857142748</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.933399456322093</v>
+        <v>-3.404084305786981</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-7.001410042071726</v>
+        <v>-6.977452633122006</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-8.047658862876247</v>
+        <v>-7.999647183885926</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-8.514727506662986</v>
+        <v>-8.946249175038609</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-10.49878658626247</v>
+        <v>-10.42552947648299</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-9.425628459515515</v>
+        <v>-9.326281134220942</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.341868079314274</v>
+        <v>-3.761190812526259</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-5.749797619266651</v>
+        <v>-5.626100998238407</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.246871549503133</v>
+        <v>-4.098182001725306</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.463443591584294</v>
+        <v>-5.291444832017525</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.01796</t>
+          <t>X ≈ -0.0179</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.29392416061556</v>
+        <v>-2.712540974684643</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.279093993516874</v>
+        <v>-3.486001460650215</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-5.29988163843452</v>
+        <v>-5.094314347750256</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.3241280395616</v>
+        <v>-1.725563909774444</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.675425722738687</v>
+        <v>-3.429387949511785</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.565043563022122</v>
+        <v>-1.942027531907435</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.869266117410426</v>
+        <v>-3.21725851991841</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2712941107903859</v>
+        <v>0.3654917156497604</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.145284397394647</v>
+        <v>-0.8860557922724652</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3691869335619913</v>
+        <v>-0.09045117470697761</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.386896221903392</v>
+        <v>-1.104308221433257</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.19804652483262</v>
+        <v>-3.880149581234349</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.431205508227336</v>
+        <v>-5.085024106988556</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-5.205469858000804</v>
+        <v>-4.835979244973096</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.01128</t>
+          <t>X ≈ -0.01122</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.480916030534274</v>
+        <v>-3.219331683042853</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.449244980741035</v>
+        <v>-4.802508768198784</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.201159222638928</v>
+        <v>-5.550856685591583</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.999505507622004</v>
+        <v>-4.002532928064852</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.394937917860553</v>
+        <v>-2.71873242362669</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.04529325463159495</v>
+        <v>-0.318287330339686</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.7537028189202104</v>
+        <v>-1.44277320679911</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.006485748421227</v>
+        <v>-3.327045683494589</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.281753619229804</v>
+        <v>-0.881748789085286</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3459581298452932</v>
+        <v>-0.2871376535882106</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.5506592881054075</v>
+        <v>-0.8458880302023104</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.1980045785354747</v>
+        <v>0.6307184234746401</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.277853725222144</v>
+        <v>2.363220071378983</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.075017946877239</v>
+        <v>1.193825217082214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.004598</t>
+          <t>X ≈ -0.00455</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-8.162734212352603</v>
+        <v>-7.652968967744194</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-3.808011214507275</v>
+        <v>-3.236146052899912</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.214146235625947</v>
+        <v>-1.629884041214616</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.072557455674016</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-5.747210645133279</v>
+        <v>-5.703534855237635</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.16574570640735</v>
+        <v>-5.145035050704422</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-7.239092429309814</v>
+        <v>-6.919976854215662</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.592524709460321</v>
+        <v>-2.528666757456087</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.358052320528486</v>
+        <v>-4.279925080878598</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-6.060243844131072</v>
+        <v>-5.675182233122143</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-6.264945002391265</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-4.526021395490361</v>
+        <v>-4.67829880043621</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.24162679425838</v>
+        <v>-3.073456727000035</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.015891144031848</v>
+        <v>-2.824411864984668</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.002084</t>
+          <t>X ≈ 0.002126</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>4.078850733314042</v>
+        <v>3.594539337903711</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4268483137195318</v>
+        <v>0.2671762062361651</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.425649018557301</v>
+        <v>-1.580050154171559</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.461604632986301</v>
+        <v>-2.03156146179402</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.08444229103839973</v>
+        <v>0.09546846702149736</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.6617038299164264</v>
+        <v>-0.5038390374153892</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1282213793305189</v>
+        <v>0.3075978966150998</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.338847264456156</v>
+        <v>-0.1582348637683779</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.932532095056061</v>
+        <v>1.839676248025128</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>0.7251499927915361</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.169457329970314</v>
+        <v>1.102404894092594</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.03765472430814754</v>
+        <v>-0.002219066216937904</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.131767266031503</v>
+        <v>-2.141563039292329</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.031396047291842</v>
+        <v>-1.020425154021275</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.008767</t>
+          <t>X ≈ 0.008802</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.042067109671038</v>
+        <v>-0.6985176219884366</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.293540972518926</v>
+        <v>-2.28169470714429</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.249463436410736</v>
+        <v>-1.226157333140144</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.558087213685724</v>
+        <v>-2.907867494824025</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.89493791786051</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.316988348656956</v>
+        <v>-5.298244160435267</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-3.962849787060058</v>
+        <v>-3.909624887341977</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.509055121494278</v>
+        <v>-5.462414169464452</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.649173968664542</v>
+        <v>-6.586343300340459</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.981107153483443</v>
+        <v>-4.511621156517755</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-5.905232772175374</v>
+        <v>-5.440399285213104</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.15143015938839</v>
+        <v>-4.657594866688797</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.132732091838498</v>
+        <v>-3.603477430933864</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.547284211396132</v>
+        <v>-2.992113728338616</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.01545</t>
+          <t>X ≈ 0.01548</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.160403210021535</v>
+        <v>-2.8285831624666</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.318154286658192</v>
+        <v>1.63919516639028</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.602870081390336</v>
+        <v>0.9269858404959592</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1899816980982649</v>
+        <v>-0.8539581437670662</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.7282712511939238</v>
+        <v>-1.343207284718986</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2101284194667699</v>
+        <v>0.2034635844184152</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.4459308807135969</v>
+        <v>0.4612788327725355</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.9826762246116303</v>
+        <v>-0.95996794034955</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.966735304211333</v>
+        <v>-2.907768574964052</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.137166921054124</v>
+        <v>-4.368539830938268</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.700842438288632</v>
+        <v>-3.61726626573558</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.666464285933309</v>
+        <v>-3.877570865950311</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-5.048153600785142</v>
+        <v>-5.228142805252986</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-7.066007694148389</v>
+        <v>-7.208397306294948</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.02213</t>
+          <t>X ≈ 0.02216</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.593850324605832</v>
+        <v>4.093661760018676</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.982664231542003</v>
+        <v>2.510484674862823</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.0302604480330686</v>
+        <v>0.5444196425229606</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.1510408881293515</v>
+        <v>0.3598382749326063</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.000856920975821</v>
+        <v>-0.4438762748243406</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.7034828913407338</v>
+        <v>-0.8000215736154743</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.1651402911053808</v>
+        <v>-0.2317468452308376</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.255261894393641</v>
+        <v>-1.326510423224278</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.316244050916417</v>
+        <v>-1.363483032361074</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.6085304484923384</v>
+        <v>-0.3005191603458712</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.370864005506469</v>
+        <v>-2.391452060712147</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.959538812652703</v>
+        <v>-2.647750732152289</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.068163186215372</v>
+        <v>-2.728443249911081</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.907848096736465</v>
+        <v>-1.536002161480624</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.02881</t>
+          <t>X ≈ 0.02883</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>229</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.977599253308441</v>
+        <v>2.948403458955809</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.859862941904005</v>
+        <v>4.858676155459349</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.901772779856337</v>
+        <v>4.901619389852016</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.975229364492783</v>
+        <v>1.97473487211478</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.057027147641634</v>
+        <v>4.105573067407406</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.791082399984148</v>
+        <v>4.815039808933761</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.889778154255048</v>
+        <v>6.937789833245368</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.169434401298098</v>
+        <v>8.218681963691814</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>10.29185835831238</v>
+        <v>10.36511546809208</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.005258339275102</v>
+        <v>9.104605664569675</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7.927194735600068</v>
+        <v>8.027102771618743</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.398254110662812</v>
+        <v>8.521950731691057</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.541422034641926</v>
+        <v>7.690111582419753</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.330476462161094</v>
+        <v>7.502475221727757</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.03549</t>
+          <t>X ≈ 0.03551</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>181</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.662730378305397</v>
+        <v>1.633534583952766</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.36646141231342</v>
+        <v>3.365274625868764</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.419203839713141</v>
+        <v>2.41905044970882</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.101915171146743</v>
+        <v>3.10142067876874</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.773570369432271</v>
+        <v>4.822116289198043</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.518458211222054</v>
+        <v>4.542415620171667</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.881261664110603</v>
+        <v>3.929273343100924</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.861706832478475</v>
+        <v>2.910954394872192</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.353210863801053</v>
+        <v>3.426467973580749</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.608264443161779</v>
+        <v>3.707611768456353</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.298590909211001</v>
+        <v>2.398498945229676</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.780482873721027</v>
+        <v>1.904179494749272</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.84961273097354</v>
+        <v>-0.7009231831957123</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.6238770807470928</v>
+        <v>-0.4518783211804305</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.04218</t>
+          <t>X ≈ 0.04219</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>154</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6.609993060374777</v>
+        <v>6.580797266022145</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.401404369908313</v>
+        <v>2.400217583463657</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.734260726144235</v>
+        <v>4.733766233766232</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.144023121100481</v>
+        <v>6.192569040866253</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>9.688150397488826</v>
+        <v>9.712107806438439</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>12.20084263562529</v>
+        <v>12.24885431461561</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>10.43507269313725</v>
+        <v>10.48432025553097</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>11.02344118596508</v>
+        <v>11.09669829574478</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.57611979223266</v>
+        <v>7.675467117527234</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.072717335271136</v>
+        <v>6.172625371289811</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.159043539574519</v>
+        <v>4.282740160602764</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.336295283663738</v>
+        <v>6.484984831441565</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.964628336487671</v>
+        <v>4.136627096054333</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>141</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.835525959612404</v>
+        <v>-2.864721753965036</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1913929037400237</v>
+        <v>-0.1925796901846795</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.713823862963153</v>
+        <v>-2.713977252967474</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.165159003062733</v>
+        <v>-1.165653495440736</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.121888272470443</v>
+        <v>-3.073342352704671</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.115294384679366</v>
+        <v>-2.091336975729753</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.07234516947745107</v>
+        <v>-0.0243334904871304</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.297465619359933</v>
+        <v>2.34671318175365</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.782582753617291</v>
+        <v>5.855839863396987</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>11.31564268069168</v>
+        <v>11.41499000598625</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>11.82016138058752</v>
+        <v>11.9200694166062</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>13.27297924925491</v>
+        <v>13.39667587028315</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>14.27126811225355</v>
+        <v>14.41995766003138</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>13.78778390432405</v>
+        <v>13.95978266389071</v>
       </c>
     </row>
     <row r="30">
@@ -1820,257 +1820,257 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>9.057545507927244</v>
+        <v>8.654936718802389</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>9.369436337940257</v>
+        <v>9.013507206461988</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>10.89774187626217</v>
+        <v>10.56151679096286</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>11.02796701985053</v>
+        <v>10.69140083217754</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>11.45121592829323</v>
+        <v>11.17302547763332</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>13.67166688100531</v>
+        <v>13.38755856926784</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.779264214046826</v>
+        <v>8.472533548003547</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.389118647183111</v>
+        <v>6.064953214804603</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.481982644506537</v>
+        <v>2.144485460036798</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.478217694330532</v>
+        <v>6.175025811260646</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.273516536070339</v>
+        <v>5.000011577316791</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.07712545765643</v>
+        <v>10.88342103312832</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>18.34928229665066</v>
+        <v>18.25525339782657</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>19.5365564084157</v>
+        <v>20.4460458326575</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.06223</t>
+          <t>X ≈ 0.06221</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.281970567403761</v>
+        <v>6.673561644500737</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>9.825423649597688</v>
+        <v>10.19242537567145</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>14.58529144010038</v>
+        <v>14.90072820368327</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>17.80830008884339</v>
+        <v>18.09183673469387</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>14.17722703059302</v>
+        <v>14.541363103946</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>15.50552889527968</v>
+        <v>15.83455678603028</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16.45174637106507</v>
+        <v>16.79430886007012</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>18.04653339738142</v>
+        <v>18.36929242621739</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>12.83091206560094</v>
+        <v>13.23027900075409</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>13.0119211043226</v>
+        <v>12.40645041993908</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.83814778111395</v>
+        <v>14.2431262989336</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>14.90345376852083</v>
+        <v>15.32170119956377</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>13.45237508015586</v>
+        <v>13.90613510973463</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.67811073038239</v>
+        <v>13.13477180848472</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.06891</t>
+          <t>X ≈ 0.06889</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>57</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.905048881746396</v>
+        <v>1.875853087393764</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.214909141141995</v>
+        <v>-3.21609592758665</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.653477368839759</v>
+        <v>1.653323978835438</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.53808847734043</v>
+        <v>3.537593984962427</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2.999798924244757</v>
+        <v>3.048344844010529</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-3.720370905769322</v>
+        <v>-3.696413496819709</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-2.050695300123216</v>
+        <v>-2.002683621132896</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.254165880651456</v>
+        <v>6.303413443045173</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.8243601355205001</v>
+        <v>-0.7511030257408038</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.83449299797428</v>
+        <v>1.933840323268853</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.629791839714088</v>
+        <v>1.729699875732763</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.172941921893951</v>
+        <v>5.296638542922196</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.77033492822966</v>
+        <v>11.91902447600749</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.24168461354395</v>
+        <v>10.41368337311061</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.07559</t>
+          <t>X ≈ 0.07557</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>65</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9.057545507927209</v>
+        <v>9.028349713574578</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.446359414863359</v>
+        <v>7.445172628418703</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.51312649164678</v>
+        <v>5.512973101642459</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>11.79719778908129</v>
+        <v>11.79670329670328</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.181985159062521</v>
+        <v>8.230531078828292</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.7870514963899211</v>
+        <v>0.8110089053395342</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.7023411371237742</v>
+        <v>0.7503528161140949</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.312195570260094</v>
+        <v>3.361443132653811</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>7.866598029121924</v>
+        <v>7.939855138901621</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.555140771253591</v>
+        <v>8.654488096548164</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.35043961299337</v>
+        <v>8.450347649012045</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5.307894688425662</v>
+        <v>5.431591309453907</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>3.349282296650713</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.4980948699541443</v>
+        <v>0.6700936295208066</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.08227</t>
+          <t>X ≈ 0.08224</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.519083969465605</v>
+        <v>3.900144585369389</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>18.40789787640182</v>
+        <v>20.2656854489315</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>15.51312649164678</v>
+        <v>17.30784489651425</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>18.14335163523513</v>
+        <v>20.00183150183148</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>12.60506208213943</v>
+        <v>14.38437723267447</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.402436111774556</v>
+        <v>6.964855059185687</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12.81772575250832</v>
+        <v>14.59650666226786</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.35065710872164</v>
+        <v>14.13067390188457</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>12.28967495219885</v>
+        <v>14.09370129274777</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.439756155868992</v>
+        <v>8.141667583727667</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.735054997608813</v>
+        <v>7.937527136191619</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.769433149964122</v>
+        <v>5.431591309453907</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>8.349282296650713</v>
+        <v>10.1646385110952</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.57501794687726</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
   </sheetData>
@@ -2210,1197 +2210,1197 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.1082</t>
+          <t>X &gt; -0.108</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4095</v>
+        <v>4105</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.002044047362439017</v>
+        <v>0.01538598958605775</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.01369939654680508</v>
+        <v>-0.02479243202486714</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.02998115569857163</v>
+        <v>-0.0409627584158585</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1300953805992009</v>
+        <v>-0.1408609616386158</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1191094578215655</v>
+        <v>-0.130786747730177</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.07648175320230877</v>
+        <v>-0.08782967402421349</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1479007711386373</v>
+        <v>-0.1595543972950892</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01644847528226734</v>
+        <v>-0.02833663270368447</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.0395933404840747</v>
+        <v>-0.05190978716987615</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.09537436376994179</v>
+        <v>-0.1078909213674635</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1400060077596805</v>
+        <v>-0.1523787385244262</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2383774431527925</v>
+        <v>-0.2510143731517829</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2298192658492866</v>
+        <v>-0.2428951794389747</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1856658138065157</v>
+        <v>-0.1993901145061514</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.1015</t>
+          <t>X &gt; -0.1014</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4089</v>
+        <v>4100</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.005675875852773515</v>
+        <v>0.006299553668810631</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.007732457663038872</v>
+        <v>-0.007685797202370281</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.02345887420687376</v>
+        <v>-0.02339274608315378</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1483048663506139</v>
+        <v>-0.147897115050398</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1609213244003271</v>
+        <v>-0.1615538379584933</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1186768977446278</v>
+        <v>-0.1188839865786804</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.1900867474916339</v>
+        <v>-0.1906297464901101</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.05776779970327794</v>
+        <v>-0.05869250375071289</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.0808673047625561</v>
+        <v>-0.08225673217491902</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1354942716902485</v>
+        <v>-0.1373097741970568</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2043389417851458</v>
+        <v>-0.2059826158972697</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2540329952326559</v>
+        <v>-0.2560657433908631</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.2692996104397452</v>
+        <v>-0.271840396488308</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.24987811572975</v>
+        <v>-0.2529832935560847</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.09481</t>
+          <t>X &gt; -0.09468</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4072</v>
+        <v>4083</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.04517551645846396</v>
+        <v>-0.04429151238698381</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.07643121272649012</v>
+        <v>-0.07619489294881987</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1395798517281932</v>
+        <v>-0.1392008114010252</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1675253858329668</v>
+        <v>-0.1670622316847599</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.202460583873787</v>
+        <v>-0.2031857419853011</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1612893784215501</v>
+        <v>-0.1614823042575253</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2571700552876592</v>
+        <v>-0.2577344511419</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1223688844122606</v>
+        <v>-0.1233283932035576</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.07174275690097431</v>
+        <v>-0.0734671552425894</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1721182307845908</v>
+        <v>-0.1742559511829</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3140247569924313</v>
+        <v>-0.3157956545761422</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.3640965505758871</v>
+        <v>-0.3663561531202433</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.3040444895019974</v>
+        <v>-0.3071212016047653</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2854928586237406</v>
+        <v>-0.2892311505240031</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.08813</t>
+          <t>X &gt; -0.08801</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4053</v>
+        <v>4064</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.02149645355451213</v>
+        <v>-0.02053615650336837</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.003838835811414754</v>
+        <v>0.00386516257737668</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.08234594929810157</v>
+        <v>-0.08211892289741485</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1356294132512019</v>
+        <v>-0.1352479135984339</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1928207342071744</v>
+        <v>-0.1938017697618619</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1282213617541572</v>
+        <v>-0.1286163024585676</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1502545430581321</v>
+        <v>-0.1513345409896445</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.0372463157671703</v>
+        <v>-0.03867026745959379</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.010719330699132</v>
+        <v>-0.01295882030211004</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1322182094255595</v>
+        <v>-0.13493781677154</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.2738207420361718</v>
+        <v>-0.2761753976486432</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.324278317360168</v>
+        <v>-0.3272342231050231</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2866328488845653</v>
+        <v>-0.2904660399502959</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2690481769816273</v>
+        <v>-0.2736525848946769</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.08145</t>
+          <t>X &gt; -0.08133</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4032</v>
+        <v>4043</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.0705328414119748</v>
+        <v>-0.06928342252011532</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.03747255493792778</v>
+        <v>0.03741392596209181</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.146037495491484</v>
+        <v>-0.1456356798079597</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1755498986589643</v>
+        <v>-0.1750555144337511</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1065192096200107</v>
+        <v>-0.1079912083613124</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.04310844268090364</v>
+        <v>-0.04386073748370478</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.01527746611010627</v>
+        <v>-0.01697861788403543</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.07601619737938137</v>
+        <v>0.07402173705754933</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.02871384246390107</v>
+        <v>0.02597554023941484</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.08898517217858171</v>
+        <v>-0.09235191789747432</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.230248595947586</v>
+        <v>-0.2332524878752409</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2563477127032101</v>
+        <v>-0.2601458779569512</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.216301635905694</v>
+        <v>-0.2211181654626486</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2493868150275205</v>
+        <v>-0.2549620222229265</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.07476</t>
+          <t>X &gt; -0.07465</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4020</v>
+        <v>4031</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.03856542304612987</v>
+        <v>-0.03731261618272441</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.09936613037007191</v>
+        <v>0.09914245280653233</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.08349965571120066</v>
+        <v>-0.08326638376080808</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1134721861048149</v>
+        <v>-0.1131438469968558</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.01779718815094355</v>
+        <v>-0.01965932482745103</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.02011237791157328</v>
+        <v>0.01911449126140496</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.0234620326176298</v>
+        <v>0.02150761475772356</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.06675248875143325</v>
+        <v>0.06463095300784261</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.0443333372920236</v>
+        <v>0.04132651192898606</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.04632734313697995</v>
+        <v>-0.05011584969145844</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.2122480100969</v>
+        <v>-0.2156071200661245</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2136598385987796</v>
+        <v>-0.2179537896324746</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1722297650254916</v>
+        <v>-0.1776233936666927</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2060765804859415</v>
+        <v>-0.2122985999316853</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.06808</t>
+          <t>X &gt; -0.06798</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3989</v>
+        <v>4000</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.08211543083420736</v>
+        <v>-0.08050803719697797</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.0943512630551524</v>
+        <v>0.09414877689633983</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1118735083532272</v>
+        <v>-0.1115594338848354</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1180887248548785</v>
+        <v>-0.1177413608835067</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.09253671726025203</v>
+        <v>-0.09458356706460336</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.01839808325314607</v>
+        <v>0.01721188399759654</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.002594567811954107</v>
+        <v>-0.004864015968244928</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.09471217755766759</v>
+        <v>0.09211635359163495</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.04756178244422671</v>
+        <v>0.04395578232811204</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.01215969687330443</v>
+        <v>-0.01684057478048828</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2028207538942084</v>
+        <v>-0.2070054899798279</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2045082181140501</v>
+        <v>-0.2098187547447594</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.184552289815457</v>
+        <v>-0.1911058861388213</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2454884457023496</v>
+        <v>-0.2529832935560847</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.0614</t>
+          <t>X &gt; -0.0613</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3948</v>
+        <v>3957</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1071786567969824</v>
+        <v>-0.1171647216124256</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.08856587707128938</v>
+        <v>-0.09983967849836972</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.3433666867261351</v>
+        <v>-0.3539623822285023</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3258169268068087</v>
+        <v>-0.3364723252547819</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.294331244453069</v>
+        <v>-0.3078140858406186</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1348584520686984</v>
+        <v>-0.1473769710791331</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1046313542189949</v>
+        <v>-0.1186218015991969</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.05194850726623201</v>
+        <v>-0.06603022668934955</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.07368537168778744</v>
+        <v>-0.08911236003054057</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.09972751914999378</v>
+        <v>-0.1164128026031648</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.3155779137836063</v>
+        <v>-0.33170363303919</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2670317778657108</v>
+        <v>-0.284692911503214</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.3183975412418931</v>
+        <v>-0.33729849412628</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2952961362027935</v>
+        <v>-0.2762332303769099</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.05472</t>
+          <t>X &gt; -0.05462</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3889</v>
+        <v>3897</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1598080541301528</v>
+        <v>-0.1571706484163897</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2183206972256784</v>
+        <v>-0.2176173827980179</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4709638342449338</v>
+        <v>-0.4696266936492535</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3268742374547955</v>
+        <v>-0.3259168525357481</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3891612811468192</v>
+        <v>-0.391706898248394</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.283234150166912</v>
+        <v>-0.2842338800440984</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2255570628011583</v>
+        <v>-0.2285248635832815</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.2161465911756011</v>
+        <v>-0.219234452635618</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1602093962976738</v>
+        <v>-0.1652586094719908</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2504752065988782</v>
+        <v>-0.2572307920996977</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.3636850383901731</v>
+        <v>-0.3701651715007301</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.4321610902004451</v>
+        <v>-0.4259263972559069</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.4151815758100739</v>
+        <v>-0.3963329272492402</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3437272318319415</v>
+        <v>-0.2868555029479367</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.04803</t>
+          <t>X &gt; -0.04795</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3837</v>
+        <v>3842</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.06281930666539637</v>
+        <v>-0.05874995718269815</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.07389666195969369</v>
+        <v>-0.04554630495721312</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2204843304135764</v>
+        <v>-0.1916726289570789</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1021596840466614</v>
+        <v>-0.07365376056964834</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3139904946434768</v>
+        <v>-0.2891341429922107</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2887901313913019</v>
+        <v>-0.2619181675875382</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1770659141582982</v>
+        <v>-0.1525790143314012</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.0568708933622446</v>
+        <v>-0.03252776131709112</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.0007223727303724559</v>
+        <v>0.02279689171600552</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.05130163410720456</v>
+        <v>0.071344770815152</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.1012754689014983</v>
+        <v>-0.06620731747786124</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.2232694823006653</v>
+        <v>-0.1755486889451916</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2003658659763374</v>
+        <v>-0.1398111376167392</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1570644091300508</v>
+        <v>-0.05829302806936454</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.04135</t>
+          <t>X &gt; -0.04127</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3755</v>
+        <v>3760</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1290690998939112</v>
+        <v>-0.1114900385100981</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1580245053100384</v>
+        <v>-0.1431298432347816</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.2991574753832609</v>
+        <v>-0.2838977548942694</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2077121945520872</v>
+        <v>-0.1926866237211087</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4123627648943327</v>
+        <v>-0.4022423562799702</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3931998648087571</v>
+        <v>-0.3804005344775447</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1706958604807198</v>
+        <v>-0.1612070866855433</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.04235039945645269</v>
+        <v>0.05125889310154008</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.003933569771852774</v>
+        <v>0.002374293054245413</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.001655295529147338</v>
+        <v>0.0167867967852402</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.126462978423163</v>
+        <v>-0.09275421325001787</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2252406183447988</v>
+        <v>-0.1791721960464372</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.1393994610057447</v>
+        <v>-0.08086357168419767</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1267130784223625</v>
+        <v>-0.02957903823693897</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.03467</t>
+          <t>X &gt; -0.03459</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.04933699476817566</v>
+        <v>0.03319309675173088</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2957933371996191</v>
+        <v>0.2796483836865349</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.0564937615177783</v>
+        <v>-0.09913143755974119</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.04891371020939772</v>
+        <v>-0.09187043006525641</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2418542174200198</v>
+        <v>-0.278422818127801</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1922775446131268</v>
+        <v>-0.1982625056930303</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.05672358669868061</v>
+        <v>-0.03877550190802737</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.1370007210564239</v>
+        <v>0.1833389033663053</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1035516041812272</v>
+        <v>0.1738841808558149</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.07962399727868785</v>
+        <v>0.1755921988300528</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.04247804203878047</v>
+        <v>0.05400541117288071</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.2283642068640717</v>
+        <v>-0.09255698926087064</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.04278818793078898</v>
+        <v>0.1059013598470386</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2025150927703336</v>
+        <v>-0.01503231586399778</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.02799</t>
+          <t>X &gt; -0.02792</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.01049290417355309</v>
+        <v>0.009933994127912626</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2607042910639024</v>
+        <v>0.2750869135034293</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.01951955646318737</v>
+        <v>-0.004070725341215109</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.03247883440976551</v>
+        <v>-0.01741212096411004</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.3989470816635361</v>
+        <v>-0.3347907377109323</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1588468206424238</v>
+        <v>-0.1192953936270413</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.01446210545269366</v>
+        <v>0.04920921608763251</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.2630282427422515</v>
+        <v>0.299503639892194</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1447723176055007</v>
+        <v>0.2338859433878824</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.297144472020193</v>
+        <v>0.4126354204359757</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1783539666809659</v>
+        <v>0.2944302350024444</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.01227392888737455</v>
+        <v>0.1520813607947176</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.2507714146346771</v>
+        <v>0.4157604436837659</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.01831691594941276</v>
+        <v>0.2064839078188783</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.0213</t>
+          <t>X &gt; -0.02124</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3205456016215606</v>
+        <v>0.3074331035321407</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.5363997034420152</v>
+        <v>0.5213927835301178</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2025296585164469</v>
+        <v>0.2190346307317057</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2414027923606028</v>
+        <v>0.2575388364300935</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.1750840810761503</v>
+        <v>-0.1403304690055336</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.2745432981326346</v>
+        <v>0.3152147208459866</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.494339638013841</v>
+        <v>0.5591580833415151</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.8189884120103059</v>
+        <v>0.8852838974327355</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8189075953169933</v>
+        <v>0.909231178640141</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.9129595663440142</v>
+        <v>1.029660898160209</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.4646530487659248</v>
+        <v>0.551380944075234</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.3772285214622926</v>
+        <v>0.5181678459238341</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5356403965289118</v>
+        <v>0.7017488776298819</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.3655173378638494</v>
+        <v>0.5548144524079675</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.01462</t>
+          <t>X &gt; -0.01456</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3038</v>
+        <v>3036</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6132248516249632</v>
+        <v>0.5531292818323905</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.8453567309113623</v>
+        <v>0.8474225524077639</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6480837003367057</v>
+        <v>0.6513130225910757</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.4491449202911042</v>
+        <v>0.4188782232260451</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.108353721375785</v>
+        <v>0.127257540772149</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.5044769281010559</v>
+        <v>0.4988572888400924</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8476796695590565</v>
+        <v>0.8663961930270219</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.9072733035866634</v>
+        <v>0.9275726553050632</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.9779567165174754</v>
+        <v>1.055290428249961</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.016780513999336</v>
+        <v>1.120789910676081</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.6145810015587614</v>
+        <v>0.6860829282256304</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.7477083310042829</v>
+        <v>0.8760019712558673</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.018801717322205</v>
+        <v>1.172543649435134</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.8166242668245829</v>
+        <v>0.9933935180381113</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.00794</t>
+          <t>X &gt; -0.007888</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2758</v>
+        <v>2754</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.9273508295091517</v>
+        <v>0.9394161344448904</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.382879747322775</v>
+        <v>1.42595582488817</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.24191546916672</v>
+        <v>1.286393580945294</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9007845576426874</v>
+        <v>0.8716153127917821</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.362495004546993</v>
+        <v>0.4186769924644054</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5510945599253674</v>
+        <v>0.5825300494096979</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.01025657194274</v>
+        <v>1.102847090176972</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.304609247952946</v>
+        <v>1.36323074228455</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.207368933344604</v>
+        <v>1.253636491898661</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.155129614897277</v>
+        <v>1.264956785448241</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7328795081236592</v>
+        <v>0.8429514141648724</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.8035158185645628</v>
+        <v>0.901118151529765</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.8909791784491219</v>
+        <v>1.050622534334131</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.790391405905531</v>
+        <v>0.9728700107285846</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; -0.001257</t>
+          <t>X &gt; -0.001212</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.257238582931983</v>
+        <v>2.190387343166257</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.142311841489104</v>
+        <v>2.104714417744177</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.747540456734065</v>
+        <v>1.710976429429472</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.62838904171894</v>
+        <v>1.632873781792242</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.256350527692227</v>
+        <v>1.310013991921856</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.387473518258332</v>
+        <v>1.41641015965925</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.21714387387162</v>
+        <v>2.270895501382221</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.874763509386639</v>
+        <v>1.929854754310021</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.021595151700105</v>
+        <v>2.059271496254759</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.210745349551459</v>
+        <v>2.275376359699344</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.756667632687765</v>
+        <v>1.863249223311335</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.583231986206847</v>
+        <v>1.713429271824317</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.495583211031423</v>
+        <v>1.651050047423553</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.347254023352725</v>
+        <v>1.525718869505475</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.005425</t>
+          <t>X &gt; 0.005465</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2063</v>
+        <v>2060</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.954372384395363</v>
+        <v>1.955907592588744</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.427529480861352</v>
+        <v>2.4115654588892</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.275123583260935</v>
+        <v>2.260545917176437</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.30840253198744</v>
+        <v>2.244798890429955</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.479274394306195</v>
+        <v>1.512831302876094</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.72817532651036</v>
+        <v>1.737073132374633</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.56445381843178</v>
+        <v>2.598747140236547</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.24280446693782</v>
+        <v>2.278545447814373</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.036403018122265</v>
+        <v>2.095941770716408</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.398311657565557</v>
+        <v>2.534249112231521</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.854298817288878</v>
+        <v>1.990302839452717</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.840203872213273</v>
+        <v>1.99992588749722</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.09867638293283</v>
+        <v>2.284379611418828</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.742734863988247</v>
+        <v>1.950900201589548</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.01211</t>
+          <t>X &gt; 0.01214</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.421044753779377</v>
+        <v>2.366569789462794</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.162799837186128</v>
+        <v>3.137652793993041</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.824050861394674</v>
+        <v>2.799968617337527</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.066320822910207</v>
+        <v>3.041960281870594</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.472008860850927</v>
+        <v>2.496657329259477</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.825405299449599</v>
+        <v>2.825496659737603</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.581031074637224</v>
+        <v>3.605647745400034</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.450096884631996</v>
+        <v>3.476137854971853</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.38911472810922</v>
+        <v>3.439165245835056</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.547599293123895</v>
+        <v>3.624305274885543</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.062786090045776</v>
+        <v>3.139895769053481</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.929097015510344</v>
+        <v>3.029901071440797</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.069170251832787</v>
+        <v>3.195281261468899</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.566614585532712</v>
+        <v>2.715626571914761</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.01879</t>
+          <t>X &gt; 0.01882</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.391453283790156</v>
+        <v>3.476282732936141</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.341706430373307</v>
+        <v>3.457731498120431</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.082712370804963</v>
+        <v>3.200047931574431</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.756046815140103</v>
+        <v>3.874149659863946</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.149868599451054</v>
+        <v>3.316873308027667</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.379353966492793</v>
+        <v>3.38557719419353</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.24508488353348</v>
+        <v>4.277302057349033</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.389014203086873</v>
+        <v>4.42371419492487</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.735364022124173</v>
+        <v>4.794904851094195</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.175329815067911</v>
+        <v>5.331620487966283</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.495408018654288</v>
+        <v>4.583262353355366</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.32612018322957</v>
+        <v>4.505374668951553</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.788521943629661</v>
+        <v>4.994570483884324</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.606925618296117</v>
+        <v>4.835452080593569</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.02547</t>
+          <t>X &gt; 0.02549</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1152</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.335056191687869</v>
+        <v>3.305860397335238</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.720397876401819</v>
+        <v>3.719211089957163</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.933265380535666</v>
+        <v>3.933111990531344</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.844740524124028</v>
+        <v>4.844246031746025</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.306450971028333</v>
+        <v>4.354996890794105</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.51701944510787</v>
+        <v>4.540976854057483</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.473975752508366</v>
+        <v>5.521987431498687</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.961768219832742</v>
+        <v>6.011015782226458</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.421619396643294</v>
+        <v>6.49487650642299</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.786978378091213</v>
+        <v>6.886325703385786</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.408666108719913</v>
+        <v>6.508574144738589</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.356238705519679</v>
+        <v>6.479935326547924</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.977754518872935</v>
+        <v>7.126444066650762</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.422240169099467</v>
+        <v>6.59423892866613</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.03215</t>
+          <t>X &gt; 0.03217</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>923</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.42374269102578</v>
+        <v>3.394546896673148</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.437692025914281</v>
+        <v>3.436505239469625</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.692974812340175</v>
+        <v>3.692821422335854</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.556677745744352</v>
+        <v>5.556183253366349</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.368334021467724</v>
+        <v>4.416879941233496</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.449023327375834</v>
+        <v>4.472980736325447</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.122709501154091</v>
+        <v>5.170721180144412</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.414037390411764</v>
+        <v>5.463284952805481</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.46139759575248</v>
+        <v>5.534654705532176</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.23661422737495</v>
+        <v>6.335961552669524</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>6.031913069114758</v>
+        <v>6.131821105133433</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.849606497743103</v>
+        <v>5.973303118771348</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.837906348655054</v>
+        <v>6.986595896432881</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.196903103973668</v>
+        <v>6.36890186354033</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.03884</t>
+          <t>X &gt; 0.03885</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>742</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.853315775395572</v>
+        <v>3.824119981042941</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.455067687722575</v>
+        <v>3.45388090127792</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.003692529382626</v>
+        <v>4.003539139378304</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6.155481015289048</v>
+        <v>6.154986522911045</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.269482567314654</v>
+        <v>4.318028487080426</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.432085707461866</v>
+        <v>4.456043116411479</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.425542464098669</v>
+        <v>5.47355414308899</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.036640936214887</v>
+        <v>6.085888498608604</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.975658779692111</v>
+        <v>6.048915889471807</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.877761546704576</v>
+        <v>6.97710887199915</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.942602167420119</v>
+        <v>7.042510203438795</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.842209430287575</v>
+        <v>6.96590605131582</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.713163698267962</v>
+        <v>8.86185324604579</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>7.860732232591538</v>
+        <v>8.0327309921582</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>588</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.131328867424834</v>
+        <v>3.102133073072203</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.731027128102497</v>
+        <v>3.729840341657841</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.356663906612766</v>
+        <v>4.356510516608445</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.527705376731738</v>
+        <v>6.527210884353735</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.778531469894553</v>
+        <v>3.827077389660325</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.055497336264331</v>
+        <v>3.079454745213944</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.651059085841702</v>
+        <v>3.699070764832022</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.884670714163796</v>
+        <v>4.933918276557513</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.653620530430146</v>
+        <v>4.726877640209842</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>6.694858196685317</v>
+        <v>6.79420552197989</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.170429147268663</v>
+        <v>7.270337183287339</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.544943354045756</v>
+        <v>7.668639975074001</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.335676854473832</v>
+        <v>9.484366402251659</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.881140395856839</v>
+        <v>9.053139155423501</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>447</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.013491128302341</v>
+        <v>4.98429533394971</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.968300560965581</v>
+        <v>4.967113774520925</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.586951995002487</v>
+        <v>6.586798604998165</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8.954313603915232</v>
+        <v>8.953819111537229</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.955173938962709</v>
+        <v>6.003719858728481</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.686552442870727</v>
+        <v>4.710509851820341</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.825555730136998</v>
+        <v>4.873567409127318</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.700768965544889</v>
+        <v>5.750016527938605</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.297504929827483</v>
+        <v>4.370762039607179</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.237295305757137</v>
+        <v>5.33664263105171</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.703735087094259</v>
+        <v>5.803643123112934</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.738113239449582</v>
+        <v>5.861809860477827</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.778812497992988</v>
+        <v>7.927502045770815</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.333407208622212</v>
+        <v>7.505405968188875</v>
       </c>
     </row>
     <row r="31">
@@ -3514,257 +3514,257 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.787305543809673</v>
+        <v>3.885237012322321</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.633845398267717</v>
+        <v>3.755548299259495</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.279890340043281</v>
+        <v>5.396694031875015</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.325567378675373</v>
+        <v>8.433554817275741</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.288735551527203</v>
+        <v>4.45593358330057</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.962202875622928</v>
+        <v>2.112440032352055</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.626763653383001</v>
+        <v>3.795969989638223</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.492056525631249</v>
+        <v>5.655718624603715</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.847983990099721</v>
+        <v>5.037350666629706</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.164245951787358</v>
+        <v>5.085615109070538</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.834180362040286</v>
+        <v>6.044265359208872</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.119287377369375</v>
+        <v>4.358246050062128</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.573772092569079</v>
+        <v>4.835181146754117</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.633326984778115</v>
+        <v>3.630737636676464</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.06557</t>
+          <t>X &gt; 0.06555</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>246</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.803636814994107</v>
+        <v>2.774441020641476</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.192450721930278</v>
+        <v>1.191263935485622</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.61068746725654</v>
+        <v>1.610534077252218</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.586441066129453</v>
+        <v>4.58594657375145</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.3896149276679068</v>
+        <v>0.4381608474336787</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-3.378051693103515</v>
+        <v>-3.354094284153902</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.430241727166432</v>
+        <v>-1.382230048176112</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.5417140192907297</v>
+        <v>0.5909615816844465</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.700244057889904</v>
+        <v>1.7735011676696</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.069837456682002</v>
+        <v>2.169184781976575</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.67814442850311</v>
+        <v>2.778052464521785</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.133005874426118</v>
+        <v>-0.009309253397873363</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.072859532423074</v>
+        <v>1.221549080200901</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.3274210775129944</v>
+        <v>-0.1554223179463321</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.07225</t>
+          <t>X &gt; 0.07223</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>189</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.074639525021205</v>
+        <v>3.045443730668573</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.521654490158433</v>
+        <v>2.520467703713777</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.597782576302862</v>
+        <v>1.597629186298541</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.902610894494394</v>
+        <v>4.902116402116391</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3975834205060522</v>
+        <v>-0.3490375007402804</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-3.274812565474143</v>
+        <v>-3.25085515652453</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.24312080833819</v>
+        <v>-1.19510912934787</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.181088923024404</v>
+        <v>-1.131841360630688</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.461632624156522</v>
+        <v>2.534889733936218</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.140814356927187</v>
+        <v>2.24016168222176</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.994314256868051</v>
+        <v>3.094222292886727</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.733212352681377</v>
+        <v>-1.609515731653133</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.153363205994786</v>
+        <v>-2.004673658216959</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.51492914306985</v>
+        <v>-3.342930383503187</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.07893</t>
+          <t>X &gt; 0.07891</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>124</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.0615611918246799</v>
+        <v>-0.09075698617731121</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.05984405908205304</v>
+        <v>-0.06103084552670879</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.454615443837092</v>
+        <v>-0.4547688338414133</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.288512925557718</v>
+        <v>1.288018433179715</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-5.40401550112869</v>
+        <v>-5.380058092179077</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-2.262919408781961</v>
+        <v>-2.214907729791641</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-3.536439665471924</v>
+        <v>-3.487192103078208</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3716153703817966</v>
+        <v>-0.2983582606021002</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.221534166711656</v>
+        <v>-1.122186841417083</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1866679008346139</v>
+        <v>0.2865759368532892</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-5.424115237132654</v>
+        <v>-5.300418616104409</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-5.037814477542838</v>
+        <v>-4.889124929765011</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-5.61853044021953</v>
+        <v>-5.446531680652868</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.08561</t>
+          <t>X &gt; 0.08558</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-1.290439840058163</v>
+        <v>-1.921876530769339</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-8.85400688550294</v>
+        <v>-9.387406557101656</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-8.058302079781789</v>
+        <v>-8.60467395718107</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-6.737600745717245</v>
+        <v>-7.2983193277311</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-13.22827125119388</v>
+        <v>-13.66992140985949</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-10.54994484060642</v>
+        <v>-11.04419471456997</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-9.444179009396393</v>
+        <v>-9.928380215560132</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-11.10172384365933</v>
+        <v>-11.57068356417877</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-6.400801238277339</v>
+        <v>-6.901773820374395</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-4.869767653654819</v>
+        <v>-5.37266122471879</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-3.883992621438814</v>
+        <v>-3.223860495784287</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-9.801995421464447</v>
+        <v>-10.22451728783116</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-11.41262246525405</v>
+        <v>-11.79614580263028</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-12.37736300550371</v>
+        <v>-12.72357152885021</v>
       </c>
     </row>
   </sheetData>
@@ -3904,1197 +3904,1197 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.1082</t>
+          <t>X &lt; -0.108</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0999636495819658</v>
+        <v>-0.7454059425340347</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.6698026383065852</v>
+        <v>1.200828737015989</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.465507444027736</v>
+        <v>1.983561336936575</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.35763734952085</v>
+        <v>6.819327731092436</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5.819347796425156</v>
+        <v>6.330078590140516</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>4.249922932488857</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>7.222487657270271</v>
+        <v>7.718678607969274</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.8030380611025834</v>
+        <v>1.37049290640946</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>2.509990885507953</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.6540418701547</v>
+        <v>5.215574069398862</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>6.830293092846894</v>
+        <v>7.364374798333351</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>11.62657600710698</v>
+        <v>12.12842388863942</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.20642515379357</v>
+        <v>11.7332659620756</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>9.051208423067727</v>
+        <v>9.629369647620372</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.1015</t>
+          <t>X &lt; -0.1014</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>90</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.258693808312124</v>
+        <v>-0.2878896026647553</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.3523423208462617</v>
+        <v>0.351155534401606</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.068682047202337</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.754462746346256</v>
+        <v>6.753968253968253</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.327284304361669</v>
+        <v>7.375830224127441</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.402436111774534</v>
+        <v>5.426393520724147</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.651059085841695</v>
+        <v>8.699070764832015</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.628434886499399</v>
+        <v>2.677682448893115</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.678563841087744</v>
+        <v>3.75182095086744</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.161978378091213</v>
+        <v>6.261325703385786</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.290610553164356</v>
+        <v>9.390518589183031</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.54721092774191</v>
+        <v>11.67090754877015</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>12.2381711855396</v>
+        <v>12.38686073331743</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.35279572465503</v>
+        <v>11.52479448422169</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.09481</t>
+          <t>X &lt; -0.09468</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>107</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.724691446101154</v>
+        <v>1.695495651748523</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.917243670794335</v>
+        <v>2.916056884349679</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.326210603796305</v>
+        <v>5.326057213791984</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.391015186637006</v>
+        <v>6.390520694259003</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.721884512045982</v>
+        <v>7.770430431811754</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.150099663176398</v>
+        <v>6.174057072126011</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9.803707060919578</v>
+        <v>9.851718739909899</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.663741220871152</v>
+        <v>4.712988783264869</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.733600185843706</v>
+        <v>2.806857295623402</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.556578585775526</v>
+        <v>6.655925911070099</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>11.95935406302935</v>
+        <v>12.05926209904803</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>13.86289109388935</v>
+        <v>13.9865877149176</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>11.57358136207127</v>
+        <v>11.72227090984909</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>10.86473757304547</v>
+        <v>11.03673633261213</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.08813</t>
+          <t>X &lt; -0.08801</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>126</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.693687144068825</v>
+        <v>0.6644913497161937</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1238481553442128</v>
+        <v>-0.1250349417888685</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.373510365393876</v>
+        <v>4.373015873015873</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.216173193250562</v>
+        <v>6.264719113016334</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.132594841933269</v>
+        <v>4.156552250882882</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.841535276317892</v>
+        <v>4.889546955308212</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.199863457927975</v>
+        <v>1.249111020321692</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.3452305077544082</v>
+        <v>0.4184876175341046</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.257216473329308</v>
+        <v>4.356563798623881</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.814420076973875</v>
+        <v>8.91432811299255</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>9.222298169666587</v>
+        <v>9.370987717444414</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>8.654383026242321</v>
+        <v>8.826381785808984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.08145</t>
+          <t>X &lt; -0.08133</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>147</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.940852676948644</v>
+        <v>1.911656882596013</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.030877633802262</v>
+        <v>-1.032064420246918</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.016527852190997</v>
+        <v>4.016374462186675</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.827025104622898</v>
+        <v>4.826530612244895</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.928191333840125</v>
+        <v>2.976737253605897</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.184749036944595</v>
+        <v>1.208706445894208</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4197665688348877</v>
+        <v>0.4677782478252084</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.088118401482454</v>
+        <v>-2.038870839088737</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.7885563403181521</v>
+        <v>-0.7152992305384558</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.443157516413208</v>
+        <v>2.542504841707782</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.320089011214243</v>
+        <v>6.419997047232918</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>7.034739272413105</v>
+        <v>7.15843589344135</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.934316310256158</v>
+        <v>6.083005858033985</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.840324069326229</v>
+        <v>7.012322828892891</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.07476</t>
+          <t>X &lt; -0.07465</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>159</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.9782034663209913</v>
+        <v>0.94900767196836</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.519775079573023</v>
+        <v>-2.520961866017679</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.11690007655244</v>
+        <v>2.116746686548119</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.876056037750864</v>
+        <v>2.875561545372861</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.450974031824984</v>
+        <v>0.4995199515907558</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.50951357376006</v>
+        <v>-0.4855561648104469</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.5942239330262282</v>
+        <v>-0.5462122540359076</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.690223394423029</v>
+        <v>-1.640975832029312</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.122274733335743</v>
+        <v>-1.049017623556047</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.172460558384714</v>
+        <v>1.271807883679287</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.370275123394961</v>
+        <v>5.470183159413637</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.404653275750285</v>
+        <v>5.528349896778529</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.355571604826814</v>
+        <v>4.504261152604641</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.210238072663408</v>
+        <v>5.38223683223007</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.06808</t>
+          <t>X &lt; -0.06798</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>190</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.72961028525512</v>
+        <v>1.700414490902489</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.986838965703448</v>
+        <v>-1.988025752148104</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.35523175480467</v>
+        <v>2.355078364800349</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.485456898393032</v>
+        <v>2.484962406015029</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.947167345297338</v>
+        <v>1.99571326506311</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3870375724359931</v>
+        <v>-0.3630801634863801</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.05456785777153073</v>
+        <v>0.1025795367618514</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.99144815443627</v>
+        <v>-1.942200592042553</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.9997987320116763</v>
+        <v>-0.92654162223198</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2555456295531968</v>
+        <v>0.3548929548477702</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.261370787082484</v>
+        <v>4.361278823101159</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.295748939437807</v>
+        <v>4.419445560466052</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.875598086124398</v>
+        <v>4.024287633902226</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>5.153965315298301</v>
+        <v>5.325964074864963</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.0614</t>
+          <t>X &lt; -0.0613</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.829428797051854</v>
+        <v>1.996325943353362</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.511346152263883</v>
+        <v>1.700702506266168</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.857954077853677</v>
+        <v>6.027994560869928</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.557144738683419</v>
+        <v>5.728694052728386</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.018855185587725</v>
+        <v>5.239444911776467</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.29898783591247</v>
+        <v>2.507938585101826</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.783242993887683</v>
+        <v>2.01809794652015</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.8851398673423105</v>
+        <v>1.123080636780585</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.255192193578168</v>
+        <v>1.515292577000011</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.698376845524166</v>
+        <v>1.979017644253702</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.372986032091561</v>
+        <v>5.637538140923617</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.545295218929638</v>
+        <v>4.837335779576058</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.418247813892094</v>
+        <v>5.729731501080906</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.046879418738712</v>
+        <v>4.6912227150276</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.05472</t>
+          <t>X &lt; -0.05462</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.126592501888858</v>
+        <v>2.097396707536227</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.904484907118544</v>
+        <v>2.903298120673888</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.263979733967602</v>
+        <v>6.263826343963281</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.346423307590086</v>
+        <v>4.345928815212083</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5.173321467804982</v>
+        <v>5.221867387570754</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.764210855801842</v>
+        <v>3.788168264751455</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.996906639880386</v>
+        <v>3.044918318870707</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.871134924421284</v>
+        <v>2.920382486815001</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.12755891124322</v>
+        <v>2.200816021022916</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.325421684879224</v>
+        <v>3.424769010173797</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.827205168257265</v>
+        <v>4.92711320427594</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.755734519827136</v>
+        <v>5.667873798296121</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.548595011427345</v>
+        <v>5.272715871732295</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.609500705497936</v>
+        <v>3.815276092109443</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.04803</t>
+          <t>X &lt; -0.04795</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.6982747209107316</v>
+        <v>0.650807715342907</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.82119267408968</v>
+        <v>0.5044122393824537</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.449542676617874</v>
+        <v>2.12216850394131</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.134681115003922</v>
+        <v>0.8152709359605836</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.486564972312856</v>
+        <v>3.199585013399471</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.205904319867024</v>
+        <v>2.897657888540238</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.965124596439004</v>
+        <v>1.687576511958454</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6310039295308698</v>
+        <v>0.3596747860578731</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.008012909072824925</v>
+        <v>-0.2520104667570848</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.5689143643622288</v>
+        <v>-0.7884827257329903</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.126359345434885</v>
+        <v>0.7315147577654102</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.490363382522268</v>
+        <v>1.939106782486618</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.241410576534093</v>
+        <v>1.543948855922793</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.762152449801221</v>
+        <v>0.6435684305818441</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.04135</t>
+          <t>X &lt; -0.04127</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.132137582519263</v>
+        <v>0.9782602681362675</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.385753354257297</v>
+        <v>1.255548299259488</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.622683601203889</v>
+        <v>2.489717287688968</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.820507812391313</v>
+        <v>1.689368770764119</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.613220590297949</v>
+        <v>3.525701025161034</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.444394153732574</v>
+        <v>3.333370264910194</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.494881929664537</v>
+        <v>1.412249059405667</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.370788112723595</v>
+        <v>-0.4489325381869875</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.03443019695409077</v>
+        <v>-0.02078886825401582</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.01452251100917579</v>
+        <v>-0.1469430304643424</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.112104177936665</v>
+        <v>0.8117072196739841</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.985395591278674</v>
+        <v>1.567548375643533</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.231635237827184</v>
+        <v>0.7072741700099314</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.122187758198002</v>
+        <v>0.2586446134206568</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.03467</t>
+          <t>X &lt; -0.03459</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3226426492393912</v>
+        <v>-0.213292036901116</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.93382874230322</v>
+        <v>-1.796469122056969</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3692415995604534</v>
+        <v>0.6366480133032368</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3196106280408983</v>
+        <v>0.5898536092882338</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.579882226024345</v>
+        <v>1.790776143498142</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.258291967630385</v>
+        <v>1.277457350511376</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3718773770571104</v>
+        <v>0.2502845007704479</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.8997949708443755</v>
+        <v>-1.185504581553694</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.6813395405547737</v>
+        <v>-1.126372750855673</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.5248536444939873</v>
+        <v>-1.139467947407859</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2805095430633457</v>
+        <v>-0.351083478000433</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.510781055246461</v>
+        <v>0.6015376421909409</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.283588865993778</v>
+        <v>-0.6880746671993663</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.34467059769991</v>
+        <v>0.09764282451188677</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.02799</t>
+          <t>X &lt; -0.02792</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.052344601962929</v>
+        <v>-0.0487897433117368</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.302402552782731</v>
+        <v>-1.350672876287561</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.09765371227715747</v>
+        <v>0.02001535516359354</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.1627203583341341</v>
+        <v>0.08573443481765253</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.001613806277383</v>
+        <v>1.650783143148161</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7981195650119446</v>
+        <v>0.5890526437793042</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.07276898017406808</v>
+        <v>-0.2433277243086707</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.325389067324558</v>
+        <v>-1.483074052288913</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.730556261673982</v>
+        <v>-1.159795210748726</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.50163313501379</v>
+        <v>-2.049089975450947</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.9026261618114972</v>
+        <v>-1.46418226551782</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.06220690809103502</v>
+        <v>-0.7573695157408693</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.272810726605101</v>
+        <v>-2.073456727000035</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.0931043238651128</v>
+        <v>-1.031237943055373</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.0213</t>
+          <t>X &lt; -0.02124</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>895</v>
+        <v>907</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.159330127450652</v>
+        <v>-1.097068346626116</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.942157250389805</v>
+        <v>-1.862603382295283</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.7341141264547701</v>
+        <v>-0.7833231946538319</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.87598538133944</v>
+        <v>-0.9220283533260698</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.636035533466881</v>
+        <v>0.5029529800711572</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9984498239951165</v>
+        <v>-1.130983528456177</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.799790877203385</v>
+        <v>-2.00844199957352</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.985080960090798</v>
+        <v>-3.183337388030324</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.98810282557892</v>
+        <v>-3.273032850302158</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.33499356604424</v>
+        <v>-3.710622095126226</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.699243443371159</v>
+        <v>-1.989212790548351</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.381068522276685</v>
+        <v>-1.8714466866534</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.963217703349287</v>
+        <v>-2.537270446320363</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.341183170441184</v>
+        <v>-2.008220338760061</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.01462</t>
+          <t>X &lt; -0.01456</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1141</v>
+        <v>1154</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.614364904017883</v>
+        <v>-1.438989288468818</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.227401343025768</v>
+        <v>-2.206496457212651</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.709095730575442</v>
+        <v>-1.697327327542091</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.185492847823063</v>
+        <v>-1.092538046146295</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2862422656866386</v>
+        <v>-0.3322045518351047</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.333856316423898</v>
+        <v>-1.303382727124394</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.243249857247733</v>
+        <v>-2.265614851016387</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.403048209499822</v>
+        <v>-2.427681535781211</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.592524000680733</v>
+        <v>-2.764332821541736</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.69779842928385</v>
+        <v>-2.938444014518652</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.632077869524068</v>
+        <v>-1.800300579164222</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.98734725248557</v>
+        <v>-2.300641855305209</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.710262361843156</v>
+        <v>-3.082114735658038</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.174324734980772</v>
+        <v>-2.613468562186938</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.00794</t>
+          <t>X &lt; -0.007888</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1421</v>
+        <v>1436</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.783565960799351</v>
+        <v>-1.785474143727562</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.661536875866155</v>
+        <v>-2.712073440429577</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.391901441314118</v>
+        <v>-2.448326138164042</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.736103291389604</v>
+        <v>-1.660047421458209</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6991337220563523</v>
+        <v>-0.7979490915203939</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.063624070170874</v>
+        <v>-1.111002601159512</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.951181810516843</v>
+        <v>-2.104810039048786</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.521452211530651</v>
+        <v>-2.603562735264681</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.335149732233127</v>
+        <v>-2.395915960228251</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.235682440622234</v>
+        <v>-2.419229852169771</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.419439384413671</v>
+        <v>-1.613264902439234</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.557341270274812</v>
+        <v>-1.725785388951998</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.728073540198793</v>
+        <v>-2.013510410268751</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.534060167126974</v>
+        <v>-1.865796664029631</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; -0.001257</t>
+          <t>X &lt; -0.001212</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1773</v>
+        <v>1786</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-3.04082644486806</v>
+        <v>-2.927010101707438</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.887620330881099</v>
+        <v>-2.814089799920481</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.356828665303894</v>
+        <v>-2.288918940650255</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.197366255959473</v>
+        <v>-2.185650652243091</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.696284719207348</v>
+        <v>-1.754469992523745</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.874374668685888</v>
+        <v>-1.898021194994918</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.996880989064664</v>
+        <v>-3.044747788802482</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.535514898023735</v>
+        <v>-2.588934614598948</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.735634384134102</v>
+        <v>-2.764091946955013</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.993277046156898</v>
+        <v>-3.055868585875544</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.379809867256071</v>
+        <v>-2.503773690799576</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.146059807782365</v>
+        <v>-2.303738237956175</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.028395268174542</v>
+        <v>-2.221110416343706</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.828253344718924</v>
+        <v>-2.053655186053291</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.005425</t>
+          <t>X &lt; 0.005465</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2116</v>
+        <v>2130</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.89378592250241</v>
+        <v>-1.880153822087173</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.353380319086902</v>
+        <v>-2.31924595952929</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.206666644225344</v>
+        <v>-2.175023161785845</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.239997376994395</v>
+        <v>-2.160881174899863</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.436114388448786</v>
+        <v>-1.456957682994265</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.678543172594587</v>
+        <v>-1.673700024645356</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.491977497609398</v>
+        <v>-2.505109550251426</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.180445624548874</v>
+        <v>-2.197473606038216</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.980716372647919</v>
+        <v>-2.022313839660804</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.333828749791387</v>
+        <v>-2.446369808433438</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.805294223722015</v>
+        <v>-1.922186520990429</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.79241765267988</v>
+        <v>-1.9323861764748</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.045143777983206</v>
+        <v>-2.208269356885395</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.699084132517839</v>
+        <v>-1.886786110457493</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.01211</t>
+          <t>X &lt; 0.01214</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2394</v>
+        <v>2406</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.79541540735196</v>
+        <v>-1.745332990657964</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.346466213373738</v>
+        <v>-2.314959712358799</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.096021117500825</v>
+        <v>-2.066671085366224</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.276781476245723</v>
+        <v>-2.246215704824984</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.836261263678281</v>
+        <v>-1.844321604720037</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.099645486893245</v>
+        <v>-2.08810523652523</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.66228257735419</v>
+        <v>-2.665758631493446</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.566009557945037</v>
+        <v>-2.571073770012354</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.521704789360129</v>
+        <v>-2.544782579249159</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.640727580578051</v>
+        <v>-2.682888220081246</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.280798152161751</v>
+        <v>-2.325269427974852</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.182152826663597</v>
+        <v>-2.244743983160461</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.287460918380603</v>
+        <v>-2.368251670320106</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.913703857634033</v>
+        <v>-2.013581797296737</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.01879</t>
+          <t>X &lt; 0.01882</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2706</v>
+        <v>2720</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.83729705296907</v>
+        <v>-1.869789834400336</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.81101308754225</v>
+        <v>-1.860492423952067</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.671268061168824</v>
+        <v>-1.722471790338503</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.037060735898876</v>
+        <v>-2.086080586080584</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.708934234619299</v>
+        <v>-1.786663159692438</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.834115104142931</v>
+        <v>-1.824339617105764</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.304832301306604</v>
+        <v>-2.30569637854898</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.38385616561466</v>
+        <v>-2.385495182149512</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.572921875539997</v>
+        <v>-2.586609222425125</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.813011371806283</v>
+        <v>-2.877196078307797</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.444346995746685</v>
+        <v>-2.474254740885925</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.353166554614901</v>
+        <v>-2.433100941718884</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.605649362012009</v>
+        <v>-2.698279533741257</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.507761062731028</v>
+        <v>-2.61327741120315</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.02547</t>
+          <t>X &lt; 0.02549</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3027</v>
+        <v>3038</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.263810767376462</v>
+        <v>-1.248230474510059</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.410298898853199</v>
+        <v>-1.404764319878907</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.491481803284096</v>
+        <v>-1.486042969200447</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.837715207043424</v>
+        <v>-1.830896137982755</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.634068352643155</v>
+        <v>-1.646523274760348</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.71453258674277</v>
+        <v>-1.717401620444598</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.078450911960978</v>
+        <v>-2.089106575069458</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.264410481123413</v>
+        <v>-2.274865368306465</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.439876498988482</v>
+        <v>-2.458789922904792</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.579544405002011</v>
+        <v>-2.607839319625398</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.436562164107372</v>
+        <v>-2.465595993008506</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.417427199986356</v>
+        <v>-2.455554439533948</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.654680715238321</v>
+        <v>-2.701435855472745</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.444142938487808</v>
+        <v>-2.500514564128842</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.03215</t>
+          <t>X &lt; 0.03217</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3256</v>
+        <v>3267</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.9666914970378784</v>
+        <v>-0.9552337761065033</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.9709270929984299</v>
+        <v>-0.9673358755811137</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.043347337554323</v>
+        <v>-1.039802981334965</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.570365449884271</v>
+        <v>-1.564954880334803</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.234907289989195</v>
+        <v>-1.244438396141177</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.258103103911736</v>
+        <v>-1.260629380039219</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.449053285187006</v>
+        <v>-1.457720112789637</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.531930260990208</v>
+        <v>-1.540669725462713</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.545804961937918</v>
+        <v>-1.561273316994559</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.765765316523648</v>
+        <v>-1.787860749958412</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.708332544582063</v>
+        <v>-1.730786201846534</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.657208961760858</v>
+        <v>-1.686558206982546</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.937791697822725</v>
+        <v>-1.973264385681617</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.756677384818083</v>
+        <v>-1.799356112656184</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.03884</t>
+          <t>X &lt; 0.03885</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3437</v>
+        <v>3448</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.8287421174908758</v>
+        <v>-0.8198488950979055</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.7433053709162465</v>
+        <v>-0.740687753973468</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.861583485151364</v>
+        <v>-0.8588106508871789</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.325026664735852</v>
+        <v>-1.320705610179296</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.9193140060787712</v>
+        <v>-0.9268085442330474</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.9546030754533348</v>
+        <v>-0.9567083311277003</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.168917685354586</v>
+        <v>-1.1755071415838</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.300954857586824</v>
+        <v>-1.30739121770921</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.288186756110271</v>
+        <v>-1.299824960900104</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.48308604116675</v>
+        <v>-1.49971459531384</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.497503141926089</v>
+        <v>-1.514211118792119</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.47627781252497</v>
+        <v>-1.498174576833719</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.880502461929858</v>
+        <v>-1.90649321790837</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.697021622514661</v>
+        <v>-1.728621344600178</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3591</v>
+        <v>3602</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5108827341969473</v>
+        <v>-0.5045793214291621</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.6088936861849135</v>
+        <v>-0.6068472941048171</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7111933306741562</v>
+        <v>-0.7090030954236894</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.065895796033956</v>
+        <v>-1.062569213732012</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.617160140082774</v>
+        <v>-0.6231851301911533</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.4992032324877584</v>
+        <v>-0.5015843186110303</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5966711346511673</v>
+        <v>-0.6026748710782002</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.7984949624487925</v>
+        <v>-0.8040864597050543</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.7609368386799105</v>
+        <v>-0.7705583732862209</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.095014358734623</v>
+        <v>-1.107873778958457</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.173125302892032</v>
+        <v>-1.185841404652699</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.234741634338683</v>
+        <v>-1.251154357753471</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.528223271278023</v>
+        <v>-1.547823326262552</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.454221819204626</v>
+        <v>-1.477858362961982</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3732</v>
+        <v>3743</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5984060171832155</v>
+        <v>-0.5931789175387365</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.5931704996665559</v>
+        <v>-0.591291573158685</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7866330595153883</v>
+        <v>-0.7843097965994161</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.069636071873354</v>
+        <v>-1.066442084427699</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7115644882962684</v>
+        <v>-0.7152619341288968</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.5601307331452503</v>
+        <v>-0.5613430828482322</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5768984785694613</v>
+        <v>-0.5809292351679858</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.68171314274975</v>
+        <v>-0.685584792741686</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.5140446089464561</v>
+        <v>-0.5212728473064061</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.6266250004479232</v>
+        <v>-0.6366371113104137</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.6826156851221299</v>
+        <v>-0.6925329621012963</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.6869139309142867</v>
+        <v>-0.699660616190549</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.9314570550771251</v>
+        <v>-0.9464726000159018</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.8783582589105379</v>
+        <v>-0.8963175174406786</v>
       </c>
     </row>
     <row r="31">
@@ -5208,257 +5208,257 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3836</v>
+        <v>3846</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.337502156800916</v>
+        <v>-0.3463388267009293</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3239108554069148</v>
+        <v>-0.3348648561288954</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4707570539731805</v>
+        <v>-0.4813229833977317</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.7425037989822272</v>
+        <v>-0.7523710729104991</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.3825842117487142</v>
+        <v>-0.3976241641129405</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.1750873013368093</v>
+        <v>-0.1885519904330835</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.323700216786456</v>
+        <v>-0.3389082991008507</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.4903111369837347</v>
+        <v>-0.5050797525606683</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4329233294986281</v>
+        <v>-0.4499736767905986</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4612855107976728</v>
+        <v>-0.4544030123429295</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5212617515446283</v>
+        <v>-0.5401993462114447</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.3681385019379064</v>
+        <v>-0.3896145117519154</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4088620869823316</v>
+        <v>-0.4323634817996904</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.3248777778360008</v>
+        <v>-0.3247461640709091</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.06557</t>
+          <t>X &lt; 0.06555</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3933</v>
+        <v>3944</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1747832378328908</v>
+        <v>-0.1724823075758906</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.07435814387701356</v>
+        <v>-0.07407758547256549</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.100463772044904</v>
+        <v>-0.1001748123904136</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2861436729058724</v>
+        <v>-0.2853168581544949</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.02431386915431233</v>
+        <v>-0.02726728268876144</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2108603695771265</v>
+        <v>0.2087821846917564</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.08929935656928478</v>
+        <v>0.08606140011422525</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.03383134012325684</v>
+        <v>-0.036804189644144</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.1062112844695093</v>
+        <v>-0.1104789281455396</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1293319823072778</v>
+        <v>-0.1351619696976272</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1673840267814413</v>
+        <v>-0.1731443897320375</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.008314979697289004</v>
+        <v>0.0005803538610891223</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.06708781011085563</v>
+        <v>-0.07617264226347231</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.02047942666366254</v>
+        <v>0.009694191230927629</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.07225</t>
+          <t>X &lt; 0.07223</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3990</v>
+        <v>4001</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1451678416759989</v>
+        <v>-0.1433953326099484</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1190886303448053</v>
+        <v>-0.1187063035140596</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.07547635764089478</v>
+        <v>-0.0752621924751935</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2316483647648582</v>
+        <v>-0.2309897781102066</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.01879051424747047</v>
+        <v>0.01645089467330507</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1548122998685741</v>
+        <v>0.1532580754759536</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.05878154435225014</v>
+        <v>0.05635619397374114</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.05586231392683771</v>
+        <v>0.05338607865215295</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1164577136334373</v>
+        <v>-0.1195941487054242</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1013054365195956</v>
+        <v>-0.1057154951160868</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1417293750433473</v>
+        <v>-0.1460559473915097</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.08205840046512236</v>
+        <v>0.07599262385272709</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.101975857161861</v>
+        <v>0.09467349360394905</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1664966436191051</v>
+        <v>0.1579139821249882</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.07893</t>
+          <t>X &lt; 0.07891</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4055</v>
+        <v>4066</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.001876496505957448</v>
+        <v>0.002758976780093292</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.001824603719249751</v>
+        <v>0.001855768721256368</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.01386431751986805</v>
+        <v>0.01383157601086538</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.03930519133312771</v>
+        <v>-0.03918407402215962</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1493534207221217</v>
+        <v>0.1474730325800664</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1649268821412591</v>
+        <v>0.1637523817943531</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.06907976530994375</v>
+        <v>0.06743151448420548</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1079828905487616</v>
+        <v>0.1061915080505145</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.01134982904614645</v>
+        <v>0.009087797670019881</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.03731713147875126</v>
+        <v>0.03418947624955848</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.005703996969813829</v>
+        <v>-0.008733206234900592</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1657851341889227</v>
+        <v>0.1615663491634578</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1540160244613631</v>
+        <v>0.1490660170373488</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1718120282582518</v>
+        <v>0.1661018023612755</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.08561</t>
+          <t>X &lt; 0.08558</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4095</v>
+        <v>4105</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.02638679322416237</v>
+        <v>0.03966962241754146</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1810899874317613</v>
+        <v>0.1938133488835661</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1648556684612004</v>
+        <v>0.1776961337124305</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1378705146504871</v>
+        <v>0.1507550772435309</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.2707540899367231</v>
+        <v>0.2824363927656961</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2159871719743833</v>
+        <v>0.2282413203837663</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1933961571890066</v>
+        <v>0.2052315949228145</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2273944898481801</v>
+        <v>0.2392381666152232</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1311383668329995</v>
+        <v>0.1427374147765974</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.09979518977970514</v>
+        <v>0.1111404731324228</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.07961331874105326</v>
+        <v>0.06670597423117641</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2009684196736643</v>
+        <v>0.211610413797338</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2340479216507134</v>
+        <v>0.2441968809604447</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.2538946257539223</v>
+        <v>0.2634600681978654</v>
       </c>
     </row>
   </sheetData>
